--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>75</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5340</v>
+        <v>7240</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4155</v>
+        <v>5600</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1251</v>
+        <v>1938</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>437</v>
+        <v>629</v>
       </c>
       <c r="F11" s="12" t="n">
+        <v>607</v>
+      </c>
+      <c r="G11" s="12" t="n">
         <v>409</v>
       </c>
-      <c r="G11" s="12" t="n">
-        <v>307</v>
-      </c>
       <c r="H11" s="12" t="n">
-        <v>302</v>
+        <v>434</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>387</v>
+        <v>567</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>250</v>
+        <v>364</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>275</v>
+        <v>389</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -856,12 +856,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>09684</t>
+          <t>19568</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>BARCELLONA POZZO DI GOTTO</t>
+          <t>MASCALUCIA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -871,35 +871,35 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>196</v>
+        <v>263</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>72</v>
+        <v>153</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>187</v>
+        <v>259</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>215</v>
+        <v>294</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>128</v>
+        <v>188</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>172</v>
+        <v>235</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -964,12 +964,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>08182</t>
+          <t>09684</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASTELLAMMARE DI STABIA</t>
+          <t>BARCELLONA POZZO DI GOTTO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,35 +979,35 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>187</v>
+        <v>259</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>149</v>
+        <v>231</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08046</t>
+          <t>08945</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>ANGRI</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,51 +1033,51 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>176</v>
+        <v>242</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>174</v>
+        <v>289</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>157</v>
+        <v>246</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19568</t>
+          <t>08182</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>MASCALUCIA</t>
+          <t>CASTELLAMMARE DI STABIA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,35 +1087,35 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>174</v>
+        <v>232</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>209</v>
+        <v>278</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08945</t>
+          <t>08046</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ANGRI</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,51 +1141,51 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>171</v>
+        <v>219</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>08970</t>
+          <t>08078</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CAVA DE' TIRRENI</t>
+          <t>CASORIA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,39 +1195,39 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>168</v>
+        <v>208</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>110</v>
+        <v>234</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>3</v>
+        <v>255</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>5</v>
+        <v>372</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>136</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1253,28 +1253,28 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>165</v>
+        <v>239</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>170</v>
+        <v>241</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>1</v>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>08970</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>CAVA DE' TIRRENI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,51 +1303,51 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>144</v>
+        <v>199</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>08078</t>
+          <t>55607</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CASORIA</t>
+          <t>MARIGLIANO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>183</v>
+        <v>253</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>284</v>
+        <v>177</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>101</v>
+        <v>274</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>55607</t>
+          <t>56584</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MARIGLIANO</t>
+          <t>POLIGNANO A MARE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,39 +1411,39 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>TEDONE VITO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>176</v>
+        <v>38</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>116</v>
+        <v>12</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>196</v>
+        <v>51</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1469,28 +1469,28 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>241</v>
+        <v>290</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>183</v>
+        <v>233</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>6</v>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>56584</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>POLIGNANO A MARE</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,51 +1519,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>TEDONE VITO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>25</v>
+        <v>252</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09651</t>
+          <t>56391</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA</t>
+          <t>MISTERBIANCO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>116</v>
+        <v>231</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>55710</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>MILAZZO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,23 +1627,23 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>118</v>
+        <v>185</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>32</v>
@@ -1652,10 +1652,10 @@
         <v>41</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>185</v>
+        <v>123</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>54340</t>
+          <t>09651</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>BENEVENTO</t>
+          <t>VILLAFRANCA TIRRENA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
+        <v>151</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>166</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>134</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L27" s="12" t="n">
         <v>115</v>
       </c>
-      <c r="F27" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="H27" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="I27" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>139</v>
-      </c>
       <c r="M27" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>55710</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SAN GIORGIO A CREMANO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,39 +1735,39 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
+        <v>148</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>159</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I28" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>170</v>
-      </c>
-      <c r="G28" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>79</v>
-      </c>
       <c r="J28" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>143</v>
+        <v>256</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>194</v>
+        <v>265</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>2</v>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MILAZZO</t>
+          <t>BENEVENTO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>88</v>
+        <v>173</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>56391</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MISTERBIANCO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>08444</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>AVERSA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>69</v>
+        <v>183</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>08444</t>
+          <t>09619</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>AVERSA</t>
+          <t>FIUMEFREDDO DI SICILIA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,32 +2005,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="J33" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="K33" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K33" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="L33" s="12" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>08413</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CAPUA</t>
+          <t>SAN GIORGIO A CREMANO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,39 +2059,39 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>89</v>
+        <v>232</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>91</v>
+        <v>185</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2117,31 +2117,31 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2171,47 +2171,47 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09619</t>
+          <t>08413</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>FIUMEFREDDO DI SICILIA</t>
+          <t>CAPUA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,51 +2221,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>55058</t>
+          <t>08164</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>GIARRE</t>
+          <t>POMIGLIANO D'ARCO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>33</v>
+        <v>158</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>55058</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>GIARRE</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,51 +2329,51 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>08164</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>POMIGLIANO D'ARCO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,51 +2383,51 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>09092</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>GIARRE</t>
+          <t>ANDRIA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,51 +2437,51 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>SETTE ALESSANDRO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="G41" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="M41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>94</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>09719</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>TERME VIGLIATORE</t>
+          <t>GIARRE</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>0</v>
@@ -2549,28 +2549,28 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
@@ -2584,12 +2584,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>08964</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>BATTIPAGLIA</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,51 +2599,51 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H44" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="K44" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I44" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K44" s="12" t="n">
-        <v>32</v>
-      </c>
       <c r="L44" s="12" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>09719</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>TERME VIGLIATORE</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,51 +2653,51 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>08146</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,35 +2707,35 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2746,12 +2746,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,51 +2761,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>153</v>
+        <v>95</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09092</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ANDRIA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,35 +2815,35 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
@@ -2854,12 +2854,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,51 +2869,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>35</v>
+        <v>196</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09627</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>SAN GIOVANNI LA PUNTA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,35 +2923,35 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="G50" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H50" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="J50" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="K50" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L50" s="12" t="n">
+        <v>148</v>
+      </c>
+      <c r="M50" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="J50" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K50" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="L50" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="M50" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -2962,12 +2962,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09992</t>
+          <t>08964</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>CAMPOFELICE DI ROCCELLA</t>
+          <t>BATTIPAGLIA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,51 +2977,51 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>08146</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,35 +3031,35 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3070,12 +3070,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09673</t>
+          <t>09627</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SANT'AGATA DI MILITELLO</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,32 +3085,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>0</v>
@@ -3124,12 +3124,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>09673</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LA PUNTA</t>
+          <t>SANT'AGATA DI MILITELLO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,35 +3139,35 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="K54" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L54" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="M54" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="L54" s="12" t="n">
-        <v>103</v>
-      </c>
-      <c r="M54" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3178,12 +3178,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>09992</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>CALATABIANO</t>
+          <t>CAMPOFELICE DI ROCCELLA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,32 +3193,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>0</v>
@@ -3251,31 +3251,31 @@
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>11</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -3286,12 +3286,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>59427</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>CALATABIANO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,51 +3355,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="G58" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H58" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I58" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J58" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H58" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I58" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="J58" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="K58" s="12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,51 +3409,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>08013</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>ACERRA</t>
+          <t>PATERNÒ</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,32 +3463,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="M60" s="12" t="n">
         <v>0</v>
@@ -3502,12 +3502,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,35 +3517,35 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -3556,12 +3556,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>39506</t>
+          <t>08013</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>ACERRA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,51 +3571,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>09704</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>PATERNÒ</t>
+          <t>ACQUEDOLCI</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,32 +3625,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J63" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="M63" s="12" t="n">
         <v>0</v>
@@ -3664,12 +3664,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>54798</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,51 +3679,51 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F64" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H64" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="G64" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H64" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I64" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="J64" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="M64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>54798</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,39 +3733,39 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="F65" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I65" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="J65" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K65" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L65" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F65" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="G65" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H65" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I65" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="J65" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K65" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L65" s="12" t="n">
-        <v>58</v>
-      </c>
       <c r="M65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3791,47 +3791,47 @@
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H66" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K66" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="M66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09704</t>
+          <t>39506</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>ACQUEDOLCI</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,51 +3841,51 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I67" s="12" t="n">
         <v>16</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>08979</t>
+          <t>09010</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>PADULA</t>
+          <t>BARLETTA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,51 +3895,51 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>SETTE ALESSANDRO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="M68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09010</t>
+          <t>08979</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>BARLETTA</t>
+          <t>PADULA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,32 +3949,32 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M69" s="12" t="n">
         <v>0</v>
@@ -3988,12 +3988,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09896</t>
+          <t>09315</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>CARLENTINI</t>
+          <t>CHIEUTI</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M70" s="12" t="n">
         <v>0</v>
@@ -4042,12 +4042,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09315</t>
+          <t>08647</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>CHIEUTI</t>
+          <t>CASTIGLIONE COSENTINO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,51 +4057,51 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>NEFZI DALILA</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>09242</t>
+          <t>09896</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI ROTONDO</t>
+          <t>CARLENTINI</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,29 +4111,29 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F72" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="G72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I72" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="J72" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L72" s="12" t="n">
         <v>11</v>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4169,19 +4169,19 @@
         </is>
       </c>
       <c r="E73" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="12" t="n">
         <v>14</v>
-      </c>
-      <c r="F73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="12" t="n">
-        <v>13</v>
       </c>
       <c r="J73" s="12" t="n">
         <v>1</v>
@@ -4190,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M73" s="12" t="n">
         <v>0</v>
@@ -4204,12 +4204,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09267</t>
+          <t>09242</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>LESINA</t>
+          <t>SAN GIOVANNI ROTONDO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4223,47 +4223,47 @@
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I74" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J74" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H74" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J74" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="K74" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>08647</t>
+          <t>38047</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLIONE COSENTINO</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,35 +4273,35 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>NEFZI DALILA</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
@@ -4312,12 +4312,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>09424</t>
+          <t>09267</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>MASSAFRA</t>
+          <t>LESINA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,32 +4327,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F76" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="G76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I76" s="12" t="n">
+      <c r="J76" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="J76" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="K76" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>0</v>
@@ -4366,12 +4366,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08530</t>
+          <t>09424</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>CATANZARO</t>
+          <t>MASSAFRA</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>VULCANO EMANUELE</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="M77" s="12" t="n">
         <v>0</v>
@@ -4420,12 +4420,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>54613</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>SAN NICOLA LA STRADA</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,11 +4435,11 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>TUFANO MAURIZIO</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F78" s="12" t="n">
         <v>0</v>
@@ -4457,29 +4457,29 @@
         <v>1</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="M78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>54613</t>
+          <t>08530</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SAN NICOLA LA STRADA</t>
+          <t>CATANZARO</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>TUFANO MAURIZIO</t>
+          <t>VULCANO EMANUELE</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
@@ -4499,22 +4499,22 @@
         <v>0</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="M79" s="12" t="n">
         <v>0</v>
@@ -4528,12 +4528,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>09284</t>
+          <t>19805</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>MANFREDONIA</t>
+          <t>TERMINI IMERESE</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,23 +4543,23 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>PIROZZI SEBASTIANO</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J80" s="12" t="n">
         <v>0</v>
@@ -4568,26 +4568,26 @@
         <v>0</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>19805</t>
+          <t>09284</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>TERMINI IMERESE</t>
+          <t>MANFREDONIA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,17 +4597,17 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>PIROZZI SEBASTIANO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" s="12" t="n">
         <v>0</v>
@@ -4619,17 +4619,17 @@
         <v>0</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4676,14 +4676,14 @@
         <v>0</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
         <v>0</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>0</v>
@@ -4766,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>0</v>
@@ -4820,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G85" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>389</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.1670951156812339</v>
+        <v>65</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>153</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.1830065359477124</v>
+        <v>28</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>144</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.6597222222222222</v>
+        <v>95</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>103</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.009708737864077669</v>
+        <v>1</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>147</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.01360544217687075</v>
+        <v>2</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>215</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.004651162790697674</v>
+        <v>1</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>144</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.7708333333333334</v>
+        <v>111</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>241</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.004149377593360996</v>
+        <v>1</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>134</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.007462686567164179</v>
+        <v>1</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>274</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.0072992700729927</v>
+        <v>2</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>233</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.02575107296137339</v>
+        <v>6</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>153</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.08496732026143791</v>
+        <v>13</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>109</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.009174311926605505</v>
+        <v>1</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>256</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.046875</v>
+        <v>12</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>265</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.007547169811320755</v>
+        <v>2</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>173</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0.09826589595375723</v>
+        <v>17</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>113</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.1946902654867257</v>
+        <v>22</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>185</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0.2216216216216216</v>
+        <v>41</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>113</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0.01769911504424779</v>
+        <v>2</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>119</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>0.2689075630252101</v>
+        <v>32</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>93</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0.6021505376344086</v>
+        <v>56</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>50</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>64</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>0.015625</v>
+        <v>1</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>95</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>0.2842105263157895</v>
+        <v>27</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>148</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>0.006756756756756757</v>
+        <v>1</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>99</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>0.0101010101010101</v>
+        <v>1</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>71</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>0.01408450704225352</v>
+        <v>1</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>107</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>0.02803738317757009</v>
+        <v>3</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>60</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>0.03333333333333333</v>
+        <v>2</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>23</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>0.4347826086956522</v>
+        <v>10</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         <v>54</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>0.1666666666666667</v>
+        <v>9</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>19</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>0.631578947368421</v>
+        <v>12</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>18</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>0.6666666666666666</v>
+        <v>12</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>17</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.05882352941176471</v>
+        <v>1</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>75</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7240</v>
+        <v>7709</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5600</v>
+        <v>5978</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1938</v>
+        <v>2136</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>629</v>
+        <v>663</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>607</v>
+        <v>640</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>567</v>
+        <v>599</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>389</v>
+        <v>423</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>28</v>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>103</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>1</v>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>2</v>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08046</t>
+          <t>08078</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>CASORIA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,35 +1141,35 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>44</v>
+        <v>288</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>45</v>
+        <v>398</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>215</v>
+        <v>157</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>08078</t>
+          <t>08046</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CASORIA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,39 +1195,39 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>234</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>255</v>
+        <v>50</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>372</v>
+        <v>46</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>136</v>
+        <v>196</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>144</v>
+        <v>227</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>6</v>
@@ -1265,16 +1265,16 @@
         <v>15</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>1</v>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>1</v>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>2</v>
@@ -1415,35 +1415,35 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>38</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>5</v>
@@ -1481,16 +1481,16 @@
         <v>3</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>6</v>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>MILAZZO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>252</v>
+        <v>204</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>56391</t>
+          <t>55456</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>MISTERBIANCO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>231</v>
+        <v>161</v>
       </c>
       <c r="G25" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H25" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="H25" s="12" t="n">
-        <v>28</v>
-      </c>
       <c r="I25" s="12" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>109</v>
+        <v>287</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>56391</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MILAZZO</t>
+          <t>MISTERBIANCO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>185</v>
+        <v>250</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09651</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,39 +1681,39 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>166</v>
+        <v>264</v>
       </c>
       <c r="G27" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>153</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="K27" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H27" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I27" s="12" t="n">
-        <v>134</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="L27" s="12" t="n">
-        <v>115</v>
+        <v>161</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1739,28 +1739,28 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>12</v>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>09651</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>VILLAFRANCA TIRRENA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>265</v>
+        <v>124</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>54340</t>
+          <t>08444</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>BENEVENTO</t>
+          <t>AVERSA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>136</v>
+        <v>188</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>BENEVENTO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>113</v>
+        <v>188</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>08444</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>AVERSA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,39 +1951,39 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>183</v>
+        <v>109</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2009,28 +2009,28 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SAN GIORGIO A CREMANO</t>
+          <t>MARCIANISE</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,51 +2059,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>232</v>
+        <v>154</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>185</v>
+        <v>120</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MARCIANISE</t>
+          <t>SAN GIORGIO A CREMANO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,39 +2113,39 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>138</v>
+        <v>242</v>
       </c>
       <c r="G35" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="K35" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H35" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="I35" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <v>50</v>
-      </c>
       <c r="L35" s="12" t="n">
-        <v>113</v>
+        <v>193</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2171,47 +2171,47 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>08413</t>
+          <t>08164</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CAPUA</t>
+          <t>POMIGLIANO D'ARCO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,51 +2221,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>109</v>
+        <v>209</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08164</t>
+          <t>08413</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>POMIGLIANO D'ARCO</t>
+          <t>CAPUA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>197</v>
+        <v>117</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>55058</t>
+          <t>38018</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>GIARRE</t>
+          <t>POTENZA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,51 +2329,51 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>CAMPANILE EUGENIA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>55058</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>GIARRE</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,39 +2383,39 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="F40" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="H40" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>83</v>
-      </c>
       <c r="J40" s="12" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2441,28 +2441,28 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>17</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>1</v>
@@ -2476,12 +2476,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>GIARRE</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,51 +2491,51 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>150</v>
+        <v>53</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>POTENZA</t>
+          <t>GIARRE</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,39 +2545,39 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>CAMPANILE EUGENIA</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>45</v>
+        <v>133</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2603,28 +2603,28 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>22</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J45" s="12" t="n">
         <v>24</v>
@@ -2678,7 +2678,7 @@
         <v>9</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
@@ -2692,12 +2692,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>82</v>
+        <v>174</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>22</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>64</v>
+        <v>212</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>08964</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>BATTIPAGLIA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2819,47 +2819,47 @@
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,35 +2869,35 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J49" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>196</v>
+        <v>71</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2908,12 +2908,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LA PUNTA</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>08964</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>BATTIPAGLIA</t>
+          <t>SAN GIOVANNI LA PUNTA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,35 +2977,35 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G51" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H51" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H51" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="I51" s="12" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3035,19 +3035,19 @@
         </is>
       </c>
       <c r="E52" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="H52" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="F52" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="G52" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="H52" s="12" t="n">
-        <v>64</v>
-      </c>
       <c r="I52" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J52" s="12" t="n">
         <v>14</v>
@@ -3063,19 +3063,19 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09627</t>
+          <t>09673</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>SANT'AGATA DI MILITELLO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,35 +3085,35 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -3124,12 +3124,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09673</t>
+          <t>09627</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SANT'AGATA DI MILITELLO</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,35 +3139,35 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3197,28 +3197,28 @@
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K55" s="12" t="n">
         <v>28</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>0</v>
@@ -3251,28 +3251,28 @@
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="M56" s="12" t="n">
         <v>3</v>
@@ -3286,12 +3286,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CALATABIANO</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>59427</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>CALATABIANO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,51 +3355,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,51 +3409,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>PATERNÒ</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,35 +3463,35 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -3502,12 +3502,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>09704</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>ACQUEDOLCI</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08013</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>ACERRA</t>
+          <t>PATERNÒ</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,51 +3571,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09704</t>
+          <t>08013</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>ACQUEDOLCI</t>
+          <t>ACERRA</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,17 +3625,17 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H63" s="12" t="n">
         <v>0</v>
@@ -3644,13 +3644,13 @@
         <v>29</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M63" s="12" t="n">
         <v>0</v>
@@ -3664,12 +3664,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>54798</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,51 +3679,51 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="M64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>54798</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,39 +3733,39 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
         <v>34</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H65" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="J65" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K65" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I65" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="J65" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K65" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="L65" s="12" t="n">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="M65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3791,28 +3791,28 @@
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="M66" s="12" t="n">
         <v>0</v>
@@ -3848,7 +3848,7 @@
         <v>29</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G67" s="12" t="n">
         <v>1</v>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F68" s="12" t="n">
         <v>0</v>
@@ -3911,23 +3911,23 @@
         <v>0</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J68" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3974,14 +3974,14 @@
         <v>8</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F70" s="12" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J70" s="12" t="n">
         <v>5</v>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4061,10 +4061,10 @@
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>4</v>
@@ -4073,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J71" s="12" t="n">
         <v>1</v>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4115,22 +4115,22 @@
         </is>
       </c>
       <c r="E72" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="H72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="J72" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K72" s="12" t="n">
         <v>0</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F73" s="12" t="n">
         <v>0</v>
@@ -4181,16 +4181,16 @@
         <v>0</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M73" s="12" t="n">
         <v>0</v>
@@ -4204,12 +4204,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09242</t>
+          <t>09267</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI ROTONDO</t>
+          <t>LESINA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4223,47 +4223,47 @@
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I74" s="12" t="n">
         <v>11</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>09242</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>SAN GIOVANNI ROTONDO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,51 +4273,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I75" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J75" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J75" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="K75" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>09267</t>
+          <t>38047</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>LESINA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,39 +4327,39 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
         <v>14</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4388,7 @@
         <v>12</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4460,14 +4460,14 @@
         <v>4</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="M78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M80" s="12" t="n">
         <v>1</v>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M82" s="12" t="n">
         <v>0</v>
@@ -4712,13 +4712,13 @@
         <v>0</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N85" headerRowCount="1">
-  <autoFilter ref="A10:N85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N88" headerRowCount="1">
+  <autoFilter ref="A10:N88"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N85"/>
+  <dimension ref="A1:N88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7709</v>
+        <v>8074</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5978</v>
+        <v>6262</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2136</v>
+        <v>2228</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -1234,12 +1234,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>55861</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SALERNO</t>
+          <t>MERCOGLIANO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,35 +1249,35 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
         <v>221</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>253</v>
+        <v>350</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08970</t>
+          <t>53274</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CAVA DE' TIRRENI</t>
+          <t>SALERNO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1307,47 +1307,47 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>149</v>
+        <v>253</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>142</v>
+        <v>251</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>55607</t>
+          <t>08970</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>MARIGLIANO</t>
+          <t>CAVA DE' TIRRENI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>273</v>
+        <v>149</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>108</v>
+        <v>10</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>190</v>
+        <v>18</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>296</v>
+        <v>142</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>56584</t>
+          <t>55607</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>POLIGNANO A MARE</t>
+          <t>MARIGLIANO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>TEDONE VITO</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>38</v>
+        <v>273</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>12</v>
+        <v>190</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>55</v>
+        <v>296</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>08136</t>
+          <t>56584</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>TORRE ANNUNZIATA</t>
+          <t>POLIGNANO A MARE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>TEDONE VITO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>298</v>
+        <v>38</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>243</v>
+        <v>55</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>08136</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MILAZZO</t>
+          <t>TORRE ANNUNZIATA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>204</v>
+        <v>298</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>MILAZZO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>161</v>
+        <v>204</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>287</v>
+        <v>137</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>56391</t>
+          <t>55456</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MISTERBIANCO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>250</v>
+        <v>161</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>117</v>
+        <v>287</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>56391</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>MISTERBIANCO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>55710</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>167</v>
+        <v>264</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>276</v>
+        <v>161</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09651</t>
+          <t>55710</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="G29" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>115</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>276</v>
+      </c>
+      <c r="M29" s="12" t="n">
         <v>12</v>
-      </c>
-      <c r="H29" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>140</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>124</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>08444</t>
+          <t>09651</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>AVERSA</t>
+          <t>VILLAFRANCA TIRRENA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>180</v>
+        <v>124</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>54340</t>
+          <t>08444</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>BENEVENTO</t>
+          <t>AVERSA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>145</v>
+        <v>188</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>48</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>BENEVENTO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09619</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>FIUMEFREDDO DI SICILIA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>09619</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MARCIANISE</t>
+          <t>FIUMEFREDDO DI SICILIA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,51 +2059,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>39</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SAN GIORGIO A CREMANO</t>
+          <t>MARCIANISE</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>242</v>
+        <v>154</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>193</v>
+        <v>120</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>29688</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>PATTI</t>
+          <t>SAN GIORGIO A CREMANO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>87</v>
+        <v>193</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>08164</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>POMIGLIANO D'ARCO</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,51 +2221,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>168</v>
+        <v>65</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08413</t>
+          <t>29688</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CAPUA</t>
+          <t>PATTI</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>08164</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>POTENZA</t>
+          <t>POMIGLIANO D'ARCO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,51 +2329,51 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>CAMPANILE EUGENIA</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>100</v>
+        <v>209</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>53</v>
+        <v>168</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>55058</t>
+          <t>08413</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>GIARRE</t>
+          <t>CAPUA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,51 +2383,51 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>09092</t>
+          <t>38018</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ANDRIA</t>
+          <t>POTENZA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,51 +2437,51 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>CAMPANILE EUGENIA</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>53</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>55058</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>GIARRE</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2530,12 +2530,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>09092</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>GIARRE</t>
+          <t>ANDRIA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,51 +2545,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>SETTE ALESSANDRO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="G43" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="J43" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K43" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="L43" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="M43" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="K43" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <v>133</v>
-      </c>
-      <c r="M43" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,51 +2599,51 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H44" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="K44" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I44" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="K44" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="L44" s="12" t="n">
-        <v>215</v>
+        <v>95</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>09719</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>TERME VIGLIATORE</t>
+          <t>GIARRE</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,32 +2653,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2711,47 +2711,47 @@
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>174</v>
+        <v>109</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>22</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>08964</t>
+          <t>09719</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>BATTIPAGLIA</t>
+          <t>TERME VIGLIATORE</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,32 +2761,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
@@ -2800,12 +2800,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,51 +2815,51 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>61</v>
+        <v>212</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>08964</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>BATTIPAGLIA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,35 +2869,35 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2908,12 +2908,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LA PUNTA</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,32 +2977,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>154</v>
+        <v>71</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>1</v>
@@ -3016,12 +3016,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08146</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,51 +3031,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09673</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SANT'AGATA DI MILITELLO</t>
+          <t>SAN GIOVANNI LA PUNTA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,32 +3085,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>1</v>
@@ -3124,12 +3124,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09627</t>
+          <t>08146</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,35 +3139,35 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H54" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="I54" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="J54" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K54" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="L54" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="M54" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="I54" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K54" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="L54" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="M54" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3178,12 +3178,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09992</t>
+          <t>09673</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>CAMPOFELICE DI ROCCELLA</t>
+          <t>SANT'AGATA DI MILITELLO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3197,47 +3197,47 @@
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="L55" s="12" t="n">
         <v>75</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>08423</t>
+          <t>09627</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>VAIRANO PATENORA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>09992</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>CAMPOFELICE DI ROCCELLA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>08423</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CALATABIANO</t>
+          <t>VAIRANO PATENORA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,35 +3355,35 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
@@ -3394,12 +3394,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,35 +3409,35 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -3448,12 +3448,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>59427</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>CALATABIANO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,35 +3463,35 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="G60" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H60" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I60" s="12" t="n">
-        <v>42</v>
-      </c>
       <c r="J60" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -3502,12 +3502,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09704</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>ACQUEDOLCI</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="L61" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="M61" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="M61" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>PATERNÒ</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,35 +3571,35 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -3610,12 +3610,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08013</t>
+          <t>09704</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>ACERRA</t>
+          <t>ACQUEDOLCI</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,51 +3625,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="M63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>54798</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>PATERNÒ</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,51 +3679,51 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>08013</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>ACERRA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,51 +3733,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="M65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>09298</t>
+          <t>54798</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>FOGGIA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,51 +3787,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="G66" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="M66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>39506</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,35 +3841,35 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="G67" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H67" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="I67" s="12" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3880,12 +3880,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09010</t>
+          <t>09298</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>BARLETTA</t>
+          <t>FOGGIA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,51 +3895,51 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="M68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>08979</t>
+          <t>39506</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>PADULA</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,51 +3949,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09315</t>
+          <t>09010</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>CHIEUTI</t>
+          <t>BARLETTA</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,51 +4003,51 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>SETTE ALESSANDRO</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="M70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08647</t>
+          <t>08979</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLIONE COSENTINO</t>
+          <t>PADULA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,14 +4057,14 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>NEFZI DALILA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>4</v>
@@ -4073,19 +4073,19 @@
         <v>0</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
@@ -4096,12 +4096,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>09896</t>
+          <t>09315</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>CARLENTINI</t>
+          <t>CHIEUTI</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,32 +4111,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J72" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K72" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K72" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L72" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M72" s="12" t="n">
         <v>0</v>
@@ -4150,12 +4150,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>08647</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>SIRACUSA</t>
+          <t>CASTIGLIONE COSENTINO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,51 +4165,51 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>LO MONACO GIUSEPPINA</t>
+          <t>NEFZI DALILA</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09267</t>
+          <t>09896</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>LESINA</t>
+          <t>CARLENTINI</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,51 +4219,51 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="12" t="n">
         <v>17</v>
-      </c>
-      <c r="F74" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="G74" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="12" t="n">
-        <v>11</v>
       </c>
       <c r="J74" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09242</t>
+          <t>09662</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI ROTONDO</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,51 +4273,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J75" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I75" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J75" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="K75" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,32 +4327,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="J76" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K76" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" s="12" t="n">
         <v>14</v>
-      </c>
-      <c r="F76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J76" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K76" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L76" s="12" t="n">
-        <v>21</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>0</v>
@@ -4366,12 +4366,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>09424</t>
+          <t>19873</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>MASSAFRA</t>
+          <t>SIRACUSA</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,51 +4381,51 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>LO MONACO GIUSEPPINA</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="M77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>54613</t>
+          <t>09242</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SAN NICOLA LA STRADA</t>
+          <t>SAN GIOVANNI ROTONDO</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,51 +4435,51 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>TUFANO MAURIZIO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F78" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I78" s="12" t="n">
         <v>11</v>
-      </c>
-      <c r="F78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="12" t="n">
-        <v>8</v>
       </c>
       <c r="J78" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="M78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>08530</t>
+          <t>38047</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>CATANZARO</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,32 +4489,32 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>VULCANO EMANUELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="M79" s="12" t="n">
         <v>0</v>
@@ -4528,12 +4528,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>19805</t>
+          <t>09424</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>TERMINI IMERESE</t>
+          <t>MASSAFRA</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,20 +4543,20 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>PIROZZI SEBASTIANO</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I80" s="12" t="n">
         <v>5</v>
@@ -4565,29 +4565,29 @@
         <v>0</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>09284</t>
+          <t>54613</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>MANFREDONIA</t>
+          <t>SAN NICOLA LA STRADA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,11 +4597,11 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>TUFANO MAURIZIO</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F81" s="12" t="n">
         <v>0</v>
@@ -4613,35 +4613,35 @@
         <v>0</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="M81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>54496</t>
+          <t>08530</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>GIOVINAZZO</t>
+          <t>CATANZARO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4651,23 +4651,23 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>VULCANO EMANUELE</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J82" s="12" t="n">
         <v>0</v>
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M82" s="12" t="n">
         <v>0</v>
@@ -4690,12 +4690,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09123</t>
+          <t>19805</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>TERLIZZI</t>
+          <t>TERMINI IMERESE</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4705,23 +4705,23 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>PIROZZI SEBASTIANO</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J83" s="12" t="n">
         <v>0</v>
@@ -4730,10 +4730,10 @@
         <v>0</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -4744,12 +4744,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>09125</t>
+          <t>09284</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>BITONTO</t>
+          <t>MANFREDONIA</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4759,91 +4759,253 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L84" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>54496</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>GIOVINAZZO</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>RENNA MARCO</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>09123</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>TERLIZZI</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>SETTE ALESSANDRO</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>09125</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>BITONTO</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>SETTE ALESSANDRO</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
           <t>18478</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>MADDALONI</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Cali Giuseppe</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>VIAGGI MARCO</t>
         </is>
       </c>
-      <c r="E85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="12" t="n">
+      <c r="E88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="G85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="G88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>78</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8074</v>
+        <v>8517</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6262</v>
+        <v>6611</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2228</v>
+        <v>2404</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>663</v>
+        <v>699</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>640</v>
+        <v>673</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>462</v>
+        <v>489</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>599</v>
+        <v>632</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>28</v>
@@ -929,47 +929,47 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>316</v>
+        <v>358</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>96</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09684</t>
+          <t>08182</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>BARCELLONA POZZO DI GOTTO</t>
+          <t>CASTELLAMMARE DI STABIA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,35 +979,35 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08945</t>
+          <t>09684</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ANGRI</t>
+          <t>BARCELLONA POZZO DI GOTTO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,51 +1033,51 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>183</v>
+        <v>239</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>256</v>
+        <v>107</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08182</t>
+          <t>08945</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CASTELLAMMARE DI STABIA</t>
+          <t>ANGRI</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,35 +1087,35 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>297</v>
+        <v>341</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>152</v>
+        <v>267</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08078</t>
+          <t>08046</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CASORIA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,51 +1141,51 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>288</v>
+        <v>56</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>398</v>
+        <v>47</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>157</v>
+        <v>240</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>08046</t>
+          <t>08078</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>CASORIA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,39 +1195,39 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>50</v>
+        <v>308</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>46</v>
+        <v>420</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>227</v>
+        <v>169</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1253,28 +1253,28 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>1</v>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>08970</t>
+          <t>55607</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>CAVA DE' TIRRENI</t>
+          <t>MARIGLIANO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>149</v>
+        <v>285</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>10</v>
+        <v>126</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>18</v>
+        <v>197</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>142</v>
+        <v>310</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>55607</t>
+          <t>08970</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MARIGLIANO</t>
+          <t>CAVA DE' TIRRENI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,39 +1411,39 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>273</v>
+        <v>154</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>190</v>
+        <v>19</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>296</v>
+        <v>150</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1469,28 +1469,28 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>5</v>
@@ -1535,16 +1535,16 @@
         <v>3</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>6</v>
@@ -1577,28 +1577,28 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>18</v>
@@ -1643,16 +1643,16 @@
         <v>23</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>2</v>
@@ -1685,28 +1685,28 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>250</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>28</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>1</v>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>99</v>
@@ -1751,7 +1751,7 @@
         <v>34</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>73</v>
@@ -1760,7 +1760,7 @@
         <v>10</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>13</v>
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>12</v>
@@ -1847,28 +1847,28 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -1901,28 +1901,28 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>13</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>2</v>
@@ -1955,28 +1955,28 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>17</v>
@@ -2009,31 +2009,31 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09619</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>FIUMEFREDDO DI SICILIA</t>
+          <t>SAN GIORGIO A CREMANO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,35 +2059,35 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>189</v>
+        <v>256</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>09619</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MARCIANISE</t>
+          <t>FIUMEFREDDO DI SICILIA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>154</v>
+        <v>195</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>39</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SAN GIORGIO A CREMANO</t>
+          <t>MARCIANISE</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,39 +2167,39 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>242</v>
+        <v>160</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>193</v>
+        <v>128</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2225,35 +2225,35 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2279,19 +2279,19 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>41</v>
@@ -2300,14 +2300,14 @@
         <v>25</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2333,28 +2333,28 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
@@ -2368,12 +2368,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>08413</t>
+          <t>38018</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CAPUA</t>
+          <t>POTENZA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,35 +2383,35 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>CAMPANILE EUGENIA</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2422,12 +2422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>08413</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>POTENZA</t>
+          <t>CAPUA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,39 +2437,39 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>CAMPANILE EUGENIA</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>0</v>
@@ -2507,16 +2507,16 @@
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>0</v>
@@ -2549,28 +2549,28 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>67</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H43" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="J43" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K43" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="L43" s="12" t="n">
         <v>54</v>
-      </c>
-      <c r="I43" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="K43" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <v>53</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>1</v>
@@ -2603,31 +2603,31 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2657,28 +2657,28 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>19</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
@@ -2711,19 +2711,19 @@
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>30</v>
@@ -2732,26 +2732,26 @@
         <v>9</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>09719</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>TERME VIGLIATORE</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,32 +2761,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>61</v>
+        <v>227</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
@@ -2800,12 +2800,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>09719</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>TERME VIGLIATORE</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,32 +2815,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>212</v>
+        <v>64</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
@@ -2854,12 +2854,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>08964</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>BATTIPAGLIA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,51 +2869,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>08964</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>BATTIPAGLIA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,39 +2923,39 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2981,28 +2981,28 @@
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>1</v>
@@ -3016,12 +3016,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>SAN GIOVANNI LA PUNTA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,51 +3031,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>65</v>
+        <v>126</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>100</v>
+        <v>163</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LA PUNTA</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,39 +3085,39 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
         <v>76</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>154</v>
+        <v>104</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3143,28 +3143,28 @@
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I54" s="12" t="n">
         <v>43</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>1</v>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>19</v>
@@ -3209,16 +3209,16 @@
         <v>0</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J55" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>1</v>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>3</v>
@@ -3263,16 +3263,16 @@
         <v>1</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K56" s="12" t="n">
         <v>26</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="M56" s="12" t="n">
         <v>0</v>
@@ -3305,28 +3305,28 @@
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M57" s="12" t="n">
         <v>0</v>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G58" s="12" t="n">
         <v>13</v>
@@ -3371,16 +3371,16 @@
         <v>10</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J58" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="M58" s="12" t="n">
         <v>3</v>
@@ -3394,12 +3394,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>09704</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>ACQUEDOLCI</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,51 +3409,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>CALATABIANO</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,51 +3463,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>PATERNÒ</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,51 +3571,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="G62" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H62" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H62" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="I62" s="12" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09704</t>
+          <t>59427</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>ACQUEDOLCI</t>
+          <t>CALATABIANO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,32 +3625,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="M63" s="12" t="n">
         <v>0</v>
@@ -3664,12 +3664,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>PATERNÒ</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,51 +3679,51 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I64" s="12" t="n">
         <v>44</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>08013</t>
+          <t>54798</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>ACERRA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,51 +3733,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I65" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="J65" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K65" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L65" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J65" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="12" t="n">
-        <v>46</v>
-      </c>
       <c r="M65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>54798</t>
+          <t>08013</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>ACERRA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="M66" s="12" t="n">
         <v>0</v>
@@ -3848,7 +3848,7 @@
         <v>34</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G67" s="12" t="n">
         <v>2</v>
@@ -3902,7 +3902,7 @@
         <v>34</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G68" s="12" t="n">
         <v>3</v>
@@ -3920,7 +3920,7 @@
         <v>5</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M68" s="12" t="n">
         <v>0</v>
@@ -3956,13 +3956,13 @@
         <v>29</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G69" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I69" s="12" t="n">
         <v>16</v>
@@ -4007,19 +4007,19 @@
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G70" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="H70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="12" t="n">
         <v>13</v>
-      </c>
-      <c r="H70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="12" t="n">
-        <v>12</v>
       </c>
       <c r="J70" s="12" t="n">
         <v>2</v>
@@ -4042,12 +4042,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08979</t>
+          <t>09315</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>PADULA</t>
+          <t>CHIEUTI</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,51 +4057,51 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G71" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="J71" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K71" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="L71" s="12" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="M71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>09315</t>
+          <t>08647</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>CHIEUTI</t>
+          <t>CASTIGLIONE COSENTINO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>NEFZI DALILA</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4150,12 +4150,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>08647</t>
+          <t>08979</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLIONE COSENTINO</t>
+          <t>PADULA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,14 +4165,14 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>NEFZI DALILA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G73" s="12" t="n">
         <v>4</v>
@@ -4181,35 +4181,35 @@
         <v>0</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L73" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09896</t>
+          <t>19873</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>CARLENTINI</t>
+          <t>SIRACUSA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,23 +4219,23 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>LO MONACO GIUSEPPINA</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J74" s="12" t="n">
         <v>3</v>
@@ -4244,10 +4244,10 @@
         <v>0</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -4258,12 +4258,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09662</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,32 +4273,32 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M75" s="12" t="n">
         <v>0</v>
@@ -4312,12 +4312,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>09662</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,51 +4327,51 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>09896</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>SIRACUSA</t>
+          <t>CARLENTINI</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,23 +4381,23 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>LO MONACO GIUSEPPINA</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="12" t="n">
         <v>17</v>
-      </c>
-      <c r="F77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="12" t="n">
-        <v>16</v>
       </c>
       <c r="J77" s="12" t="n">
         <v>3</v>
@@ -4406,26 +4406,26 @@
         <v>0</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="M77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>09242</t>
+          <t>38047</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI ROTONDO</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,51 +4435,51 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
         <v>15</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>09242</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>SAN GIOVANNI ROTONDO</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,39 +4489,39 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="M79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F83" s="12" t="n">
         <v>0</v>
@@ -4721,10 +4721,10 @@
         <v>0</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" s="12" t="n">
         <v>0</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4784,7 @@
         <v>1</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M84" s="12" t="n">
         <v>0</v>
@@ -4874,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G86" s="12" t="n">
         <v>0</v>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>78</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8517</v>
+        <v>9097</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6611</v>
+        <v>7082</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2404</v>
+        <v>2622</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>699</v>
+        <v>749</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>673</v>
+        <v>724</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>489</v>
+        <v>513</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>632</v>
+        <v>677</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>406</v>
+        <v>434</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>437</v>
+        <v>462</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>322</v>
+        <v>355</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>298</v>
+        <v>357</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>28</v>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>96</v>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>2</v>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>1</v>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08046</t>
+          <t>55861</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>MERCOGLIANO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,39 +1141,39 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>244</v>
+        <v>376</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>72</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1234,12 +1234,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>55861</t>
+          <t>08046</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MERCOGLIANO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,39 +1249,39 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>361</v>
+        <v>250</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>170</v>
+        <v>211</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>285</v>
+        <v>248</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>1</v>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>55607</t>
+          <t>56584</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>MARIGLIANO</t>
+          <t>POLIGNANO A MARE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>TEDONE VITO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>285</v>
+        <v>44</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>197</v>
+        <v>12</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>134</v>
+        <v>224</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>310</v>
+        <v>64</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>08970</t>
+          <t>55607</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CAVA DE' TIRRENI</t>
+          <t>MARIGLIANO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>154</v>
+        <v>301</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>14</v>
+        <v>139</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>19</v>
+        <v>208</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>150</v>
+        <v>331</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>56584</t>
+          <t>08970</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>POLIGNANO A MARE</t>
+          <t>CAVA DE' TIRRENI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,39 +1465,39 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>TEDONE VITO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>39</v>
+        <v>167</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>5</v>
@@ -1535,16 +1535,16 @@
         <v>3</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>6</v>
@@ -1577,28 +1577,28 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>47</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -1631,28 +1631,28 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>2</v>
@@ -1685,28 +1685,28 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>250</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>28</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>28</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>1</v>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>55710</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>278</v>
+        <v>183</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>159</v>
+        <v>128</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>168</v>
+        <v>303</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>55710</t>
+          <t>09651</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>VILLAFRANCA TIRRENA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>287</v>
+        <v>139</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>09651</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>190</v>
+        <v>302</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>08444</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>AVERSA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>92</v>
+        <v>161</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>189</v>
+        <v>127</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>54340</t>
+          <t>08444</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>BENEVENTO</t>
+          <t>AVERSA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>155</v>
+        <v>214</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>BENEVENTO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>114</v>
+        <v>177</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="H33" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="K33" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="I33" s="12" t="n">
-        <v>149</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="K33" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L33" s="12" t="n">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SAN GIORGIO A CREMANO</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,51 +2059,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>256</v>
+        <v>107</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>199</v>
+        <v>78</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>09619</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>FIUMEFREDDO DI SICILIA</t>
+          <t>SAN GIORGIO A CREMANO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,35 +2113,35 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>195</v>
+        <v>266</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>110</v>
+        <v>207</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2152,12 +2152,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>09619</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MARCIANISE</t>
+          <t>FIUMEFREDDO DI SICILIA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>39512</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>MARCIANISE</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,35 +2221,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
+        <v>142</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>169</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="I37" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L37" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="F37" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="G37" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="H37" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <v>104</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>70</v>
-      </c>
       <c r="M37" s="12" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2260,12 +2260,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>29688</t>
+          <t>08164</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>PATTI</t>
+          <t>POMIGLIANO D'ARCO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08164</t>
+          <t>29688</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>POMIGLIANO D'ARCO</t>
+          <t>PATTI</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,39 +2329,39 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2387,35 +2387,35 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2441,28 +2441,28 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>32</v>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>47</v>
@@ -2516,26 +2516,26 @@
         <v>6</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>09092</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>ANDRIA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,51 +2545,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>09092</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>ANDRIA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,39 +2599,39 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>SETTE ALESSANDRO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>1</v>
@@ -2669,16 +2669,16 @@
         <v>1</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
@@ -2692,12 +2692,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,35 +2707,35 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2746,12 +2746,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,51 +2761,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>227</v>
+        <v>70</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09719</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>TERME VIGLIATORE</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,32 +2815,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>64</v>
+        <v>238</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
@@ -2854,12 +2854,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>09719</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>TERME VIGLIATORE</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,26 +2869,26 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>10</v>
@@ -2901,19 +2901,19 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>08964</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>BATTIPAGLIA</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,32 +2923,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>133</v>
+        <v>240</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
@@ -2962,12 +2962,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,51 +2977,51 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="I51" s="12" t="n">
         <v>66</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>08964</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LA PUNTA</t>
+          <t>BATTIPAGLIA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,35 +3031,35 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3070,12 +3070,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>SAN GIOVANNI LA PUNTA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,51 +3085,51 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>70</v>
+        <v>141</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>08146</t>
+          <t>09673</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>SANT'AGATA DI MILITELLO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,32 +3139,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="J54" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K54" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K54" s="12" t="n">
-        <v>36</v>
-      </c>
       <c r="L54" s="12" t="n">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>1</v>
@@ -3178,12 +3178,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09673</t>
+          <t>09704</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SANT'AGATA DI MILITELLO</t>
+          <t>ACQUEDOLCI</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3197,47 +3197,47 @@
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09627</t>
+          <t>08146</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,35 +3247,35 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="H56" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="I56" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="J56" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K56" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="L56" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="M56" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="I56" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="J56" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K56" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="L56" s="12" t="n">
-        <v>111</v>
-      </c>
-      <c r="M56" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -3305,28 +3305,28 @@
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M57" s="12" t="n">
         <v>0</v>
@@ -3340,12 +3340,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>08423</t>
+          <t>09627</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>VAIRANO PATENORA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,51 +3355,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>87</v>
+        <v>168</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="J58" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>09704</t>
+          <t>08423</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>ACQUEDOLCI</t>
+          <t>VAIRANO PATENORA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,51 +3409,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>2</v>
+        <v>130</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>PATERNÒ</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,51 +3463,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>PATERNÒ</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>59427</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>CALATABIANO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,51 +3571,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>CALATABIANO</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,51 +3625,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,39 +3679,39 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3737,35 +3737,35 @@
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J65" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M66" s="12" t="n">
         <v>0</v>
@@ -3826,12 +3826,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>09298</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>FOGGIA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,32 +3841,32 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H67" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M67" s="12" t="n">
         <v>0</v>
@@ -3880,12 +3880,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09298</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>FOGGIA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,32 +3895,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H68" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="M68" s="12" t="n">
         <v>0</v>
@@ -3934,12 +3934,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>39506</t>
+          <t>09315</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>CHIEUTI</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,39 +3949,39 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J69" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F70" s="12" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J70" s="12" t="n">
         <v>2</v>
@@ -4028,26 +4028,26 @@
         <v>8</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09315</t>
+          <t>39506</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>CHIEUTI</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,39 +4057,39 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J71" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4115,35 +4115,35 @@
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J72" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="M72" s="12" t="n">
         <v>12</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F73" s="12" t="n">
         <v>0</v>
@@ -4181,10 +4181,10 @@
         <v>0</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" s="12" t="n">
         <v>8</v>
@@ -4204,12 +4204,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>09662</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>SIRACUSA</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,35 +4219,35 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>LO MONACO GIUSEPPINA</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -4277,19 +4277,19 @@
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J75" s="12" t="n">
         <v>4</v>
@@ -4298,7 +4298,7 @@
         <v>1</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M75" s="12" t="n">
         <v>0</v>
@@ -4312,12 +4312,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>09662</t>
+          <t>19873</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>SIRACUSA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,35 +4327,35 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>LO MONACO GIUSEPPINA</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F77" s="12" t="n">
         <v>0</v>
@@ -4397,7 +4397,7 @@
         <v>0</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J77" s="12" t="n">
         <v>3</v>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4439,19 +4439,19 @@
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J78" s="12" t="n">
         <v>2</v>
@@ -4496,7 +4496,7 @@
         <v>15</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G79" s="12" t="n">
         <v>0</v>
@@ -4528,12 +4528,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>09424</t>
+          <t>54613</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>MASSAFRA</t>
+          <t>SAN NICOLA LA STRADA</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,51 +4543,51 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>TUFANO MAURIZIO</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
         <v>12</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J80" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I80" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L80" s="12" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="M80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>54613</t>
+          <t>09424</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>SAN NICOLA LA STRADA</t>
+          <t>MASSAFRA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,39 +4597,39 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>TUFANO MAURIZIO</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="M81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M82" s="12" t="n">
         <v>0</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>78</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>9097</v>
+        <v>9648</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7082</v>
+        <v>7528</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2622</v>
+        <v>2838</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,35 +821,35 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>749</v>
+        <v>795</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>724</v>
+        <v>770</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>487</v>
+        <v>515</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>677</v>
+        <v>720</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>462</v>
+        <v>488</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>355</v>
+        <v>388</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>28</v>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>378</v>
+        <v>410</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>96</v>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>22</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>2</v>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09684</t>
+          <t>08945</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BARCELLONA POZZO DI GOTTO</t>
+          <t>ANGRI</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,51 +1033,51 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>313</v>
+        <v>377</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>252</v>
+        <v>203</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>112</v>
+        <v>305</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08945</t>
+          <t>09684</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ANGRI</t>
+          <t>BARCELLONA POZZO DI GOTTO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,39 +1087,39 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>366</v>
+        <v>321</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>194</v>
+        <v>269</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>291</v>
+        <v>118</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,28 +1253,28 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>1</v>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>1</v>
@@ -1361,35 +1361,35 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1415,28 +1415,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>2</v>
@@ -1469,28 +1469,28 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>1</v>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08136</t>
+          <t>56391</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>TORRE ANNUNZIATA</t>
+          <t>MISTERBIANCO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>324</v>
+        <v>263</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>261</v>
+        <v>141</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>08136</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>MILAZZO</t>
+          <t>TORRE ANNUNZIATA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,35 +1573,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>237</v>
+        <v>327</v>
       </c>
       <c r="G25" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>184</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="K25" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H25" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>136</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>47</v>
-      </c>
       <c r="L25" s="12" t="n">
-        <v>158</v>
+        <v>276</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1612,12 +1612,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>MILAZZO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>175</v>
+        <v>258</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>322</v>
+        <v>174</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>56391</t>
+          <t>09651</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>MISTERBIANCO</t>
+          <t>VILLAFRANCA TIRRENA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,46 +1681,46 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>28</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>55710</t>
+          <t>55456</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1739,47 +1739,47 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G28" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>173</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="K28" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H28" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>128</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>64</v>
-      </c>
       <c r="L28" s="12" t="n">
-        <v>303</v>
+        <v>343</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>09651</t>
+          <t>55710</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>50</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>139</v>
+        <v>321</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>302</v>
+        <v>123</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,39 +1897,39 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
+        <v>174</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>311</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="I31" s="12" t="n">
         <v>166</v>
       </c>
-      <c r="F31" s="12" t="n">
-        <v>118</v>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="I31" s="12" t="n">
-        <v>161</v>
-      </c>
       <c r="J31" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1955,28 +1955,28 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>2</v>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>54340</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>BENEVENTO</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>177</v>
+        <v>110</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>203</v>
+        <v>84</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>39512</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>BENEVENTO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,39 +2059,39 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>107</v>
+        <v>183</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2117,28 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>41</v>
@@ -2171,28 +2171,28 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
@@ -2225,47 +2225,47 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>28</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08164</t>
+          <t>29688</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>POMIGLIANO D'ARCO</t>
+          <t>PATTI</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>198</v>
+        <v>102</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>29688</t>
+          <t>08164</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PATTI</t>
+          <t>POMIGLIANO D'ARCO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,39 +2329,39 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>95</v>
+        <v>206</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2387,47 +2387,47 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>27</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>08413</t>
+          <t>55058</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>CAPUA</t>
+          <t>GIARRE</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,51 +2437,51 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>55058</t>
+          <t>08413</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>GIARRE</t>
+          <t>CAPUA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,51 +2491,51 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>GIARRE</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,51 +2545,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>62</v>
+        <v>170</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09092</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ANDRIA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,35 +2599,35 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2638,12 +2638,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>09092</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>GIARRE</t>
+          <t>ANDRIA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,51 +2653,51 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>SETTE ALESSANDRO</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>165</v>
+        <v>72</v>
       </c>
       <c r="G45" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="J45" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K45" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="L45" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="M45" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="J45" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="K45" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="L45" s="12" t="n">
-        <v>142</v>
-      </c>
-      <c r="M45" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,35 +2707,35 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2746,12 +2746,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,51 +2761,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J47" s="12" t="n">
         <v>27</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,51 +2815,51 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>238</v>
+        <v>76</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09719</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>TERME VIGLIATORE</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,32 +2869,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>146</v>
+        <v>198</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>66</v>
+        <v>263</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
@@ -2908,12 +2908,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>09719</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>TERME VIGLIATORE</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,32 +2923,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>240</v>
+        <v>74</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
@@ -2981,35 +2981,35 @@
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H51" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>30</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3035,28 +3035,28 @@
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>0</v>
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>9</v>
@@ -3101,16 +3101,16 @@
         <v>3</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>1</v>
@@ -3124,12 +3124,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09673</t>
+          <t>08146</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SANT'AGATA DI MILITELLO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,32 +3139,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>1</v>
@@ -3178,12 +3178,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09704</t>
+          <t>09673</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>ACQUEDOLCI</t>
+          <t>SANT'AGATA DI MILITELLO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3197,47 +3197,47 @@
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="J55" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K55" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K55" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="L55" s="12" t="n">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>08146</t>
+          <t>09992</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>CAMPOFELICE DI ROCCELLA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09992</t>
+          <t>09704</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CAMPOFELICE DI ROCCELLA</t>
+          <t>ACQUEDOLCI</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3305,28 +3305,28 @@
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>84</v>
+        <v>2</v>
       </c>
       <c r="M57" s="12" t="n">
         <v>0</v>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G58" s="12" t="n">
         <v>3</v>
@@ -3371,16 +3371,16 @@
         <v>2</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K58" s="12" t="n">
         <v>26</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="M58" s="12" t="n">
         <v>0</v>
@@ -3413,28 +3413,28 @@
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I59" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="J59" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K59" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J59" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K59" s="12" t="n">
-        <v>30</v>
-      </c>
       <c r="L59" s="12" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="M59" s="12" t="n">
         <v>3</v>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>1</v>
@@ -3479,16 +3479,16 @@
         <v>2</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K60" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M60" s="12" t="n">
         <v>0</v>
@@ -3502,12 +3502,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CALATABIANO</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,51 +3571,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,51 +3625,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>59427</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>CALATABIANO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,39 +3679,39 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
         <v>49</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G65" s="12" t="n">
         <v>4</v>
@@ -3758,14 +3758,14 @@
         <v>21</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3791,28 +3791,28 @@
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M66" s="12" t="n">
         <v>0</v>
@@ -3845,28 +3845,28 @@
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G67" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="M67" s="12" t="n">
         <v>0</v>
@@ -3899,19 +3899,19 @@
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="G68" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J68" s="12" t="n">
         <v>17</v>
@@ -3920,7 +3920,7 @@
         <v>4</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="M68" s="12" t="n">
         <v>0</v>
@@ -3953,35 +3953,35 @@
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4028,14 +4028,14 @@
         <v>8</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>29</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>1</v>
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G72" s="12" t="n">
         <v>6</v>
@@ -4127,7 +4127,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J72" s="12" t="n">
         <v>1</v>
@@ -4150,12 +4150,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>08979</t>
+          <t>09662</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>PADULA</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
@@ -4175,41 +4175,41 @@
         <v>0</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="J73" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="J73" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L73" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="M73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09662</t>
+          <t>08979</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>PADULA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,51 +4219,51 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H74" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="J74" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="M74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>19873</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SIRACUSA</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>LO MONACO GIUSEPPINA</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
@@ -4283,7 +4283,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H75" s="12" t="n">
         <v>0</v>
@@ -4295,13 +4295,13 @@
         <v>4</v>
       </c>
       <c r="K75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="M75" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="L75" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
@@ -4312,12 +4312,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SIRACUSA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,35 +4327,35 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>LO MONACO GIUSEPPINA</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4460,14 +4460,14 @@
         <v>2</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4568,14 +4568,14 @@
         <v>4</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4604,13 +4604,13 @@
         <v>12</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I81" s="12" t="n">
         <v>5</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4874,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G86" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N88" headerRowCount="1">
-  <autoFilter ref="A10:N88"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O88" headerRowCount="1">
+  <autoFilter ref="A10:O88"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:O88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>SS 87 KM.25+340  VIALE DELLA LIBERTA, 4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>MIELE NICOLINA</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>795</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>770</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>515</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>541</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>720</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>460</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>488</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA ALCIDE DE GASPERI</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>388</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>389</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>285</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>198</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>S MARIA DEL POZZO</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>MIELE NICOLINA</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>330</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>410</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>196</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>295</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>175</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIALE EUROPA 87</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>MIELE NICOLINA</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>305</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>355</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>236</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>179</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>STR PROV ACC AUTOSTR</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>ASCIONE DANIELE</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>301</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>377</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>203</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>305</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA PAPA GIOVANNI XXIII N.51.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>CASSATA FULVIA</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>298</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>321</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>122</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA N.SANTANGELO SNC</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>279</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>390</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>327</v>
       </c>
-      <c r="M17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA A.DIAZ</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>CONTE DOMENICO</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>303</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>338</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>470</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>186</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>CAIO DUILIO FUORIGRO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>262</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>280</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>223</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>263</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA MEDAGLIE D'ORO</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>ASCIONE DANIELE</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>254</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>312</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>153</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>293</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>SS ADRIATICA KM 838+890</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>TEDONE VITO</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>241</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>232</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="M21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA 11 SETTEMBRE</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>CONTE DOMENICO</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>238</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>320</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>144</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>220</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>145</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>357</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIALE LIBERTA S S 18</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>ASCIONE DANIELE</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>225</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>165</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA CARLO MARX 60</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>208</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>263</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>175</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>141</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>CORSO UMBERTO S S 18</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>ASCIONE DANIELE</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>207</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>327</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>276</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="N25" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIALE A. GRAMSCI 156/158</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>GUARISCO ADELINO</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>202</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>258</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="I26" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="J26" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>174</v>
       </c>
-      <c r="M26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="N26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VILLAFRANCA TIRRENA SNC</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>GUARISCO ADELINO</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>222</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>152</v>
       </c>
-      <c r="M27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="N27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>MARIANO SEMMOLA 25</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>189</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="I28" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="J28" s="12" t="n">
         <v>173</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="L28" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="M28" s="12" t="n">
         <v>343</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>AGNANO ASTRONI</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>186</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>194</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>132</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>321</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="N29" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA A FALCONE 224</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>179</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="I30" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="J30" s="12" t="n">
         <v>174</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="N30" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1892,42 +2008,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>NAZIONALE 102 PER CATANIA</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>174</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>311</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="I31" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="J31" s="12" t="n">
         <v>166</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="K31" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="K31" s="12" t="n">
+      <c r="L31" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="M31" s="12" t="n">
         <v>176</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="N31" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1946,42 +2067,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIALE KENNEDY ANGOLO VIA JASI</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>CONTE DOMENICO</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>171</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>233</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="I32" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="J32" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="K32" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="K32" s="12" t="n">
+      <c r="L32" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="L32" s="12" t="n">
+      <c r="M32" s="12" t="n">
         <v>205</v>
       </c>
-      <c r="M32" s="12" t="n">
+      <c r="N32" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2000,42 +2126,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA ERNESTO  BASILE 15/17</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>167</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="I33" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="J33" s="12" t="n">
         <v>138</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="K33" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="K33" s="12" t="n">
+      <c r="L33" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="M33" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="M33" s="12" t="n">
+      <c r="N33" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2054,42 +2185,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>LOCALITA' CAPODIMONTE SNC.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>183</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="I34" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="J34" s="12" t="n">
         <v>112</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>47</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>47</v>
       </c>
       <c r="L34" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="M34" s="12" t="n">
         <v>221</v>
       </c>
-      <c r="M34" s="12" t="n">
+      <c r="N34" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2108,42 +2244,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA GIANTURCO</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>MIELE NICOLINA</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>159</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>273</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="I35" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="J35" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="K35" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="K35" s="12" t="n">
+      <c r="L35" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="L35" s="12" t="n">
+      <c r="M35" s="12" t="n">
         <v>221</v>
       </c>
-      <c r="M35" s="12" t="n">
+      <c r="N35" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2162,42 +2303,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA MARCONI</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>151</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="I36" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="J36" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="K36" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="K36" s="12" t="n">
+      <c r="L36" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="L36" s="12" t="n">
+      <c r="M36" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="M36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="N36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2216,42 +2362,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA LEONARDO DA VINCI 14</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>CONTE DOMENICO</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>182</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="I37" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="J37" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="K37" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="K37" s="12" t="n">
+      <c r="L37" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="L37" s="12" t="n">
+      <c r="M37" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="M37" s="12" t="n">
+      <c r="N37" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2270,42 +2421,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA PAPA GIOVANNI XIII  SN</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>CASSATA FULVIA</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>142</v>
       </c>
-      <c r="F38" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H38" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="12" t="n">
         <v>107</v>
       </c>
-      <c r="J38" s="12" t="n">
+      <c r="K38" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="K38" s="12" t="n">
+      <c r="L38" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="L38" s="12" t="n">
+      <c r="M38" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="M38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="N38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2324,42 +2480,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA NAZIONALE DELLE PUGLIE</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>MIELE NICOLINA</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>268</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="I39" s="12" t="n">
         <v>153</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="J39" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="J39" s="12" t="n">
+      <c r="K39" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="K39" s="12" t="n">
+      <c r="L39" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L39" s="12" t="n">
+      <c r="M39" s="12" t="n">
         <v>206</v>
       </c>
-      <c r="M39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="N39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2378,42 +2539,47 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA APPIA 187</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>CAMPANILE EUGENIA</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>131</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="H40" s="12" t="n">
+      <c r="I40" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I40" s="12" t="n">
+      <c r="J40" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="J40" s="12" t="n">
+      <c r="K40" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="K40" s="12" t="n">
+      <c r="L40" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="L40" s="12" t="n">
+      <c r="M40" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="M40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="N40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2432,42 +2598,47 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA LUIGI STURZO SN</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="F41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="12" t="n">
         <v>107</v>
       </c>
-      <c r="J41" s="12" t="n">
+      <c r="K41" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="K41" s="12" t="n">
+      <c r="L41" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="M41" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="M41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="N41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2486,42 +2657,47 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA FUORI PORTA ROMA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>142</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="H42" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="H42" s="12" t="n">
+      <c r="I42" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="I42" s="12" t="n">
+      <c r="J42" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="J42" s="12" t="n">
+      <c r="K42" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="K42" s="12" t="n">
+      <c r="L42" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="L42" s="12" t="n">
+      <c r="M42" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="M42" s="12" t="n">
+      <c r="N42" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2540,42 +2716,47 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>PROVINCIALE MACCHIA DI GIARRE</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
           <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="H43" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="12" t="n">
+      <c r="I43" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="12" t="n">
+      <c r="J43" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="J43" s="12" t="n">
+      <c r="K43" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="K43" s="12" t="n">
+      <c r="L43" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="L43" s="12" t="n">
+      <c r="M43" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="M43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="N43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2594,42 +2775,47 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>STADERA POGGIOREALE</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="H44" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="H44" s="12" t="n">
+      <c r="I44" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I44" s="12" t="n">
+      <c r="J44" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="J44" s="12" t="n">
+      <c r="K44" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="K44" s="12" t="n">
+      <c r="L44" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L44" s="12" t="n">
+      <c r="M44" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="M44" s="12" t="n">
+      <c r="N44" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2648,42 +2834,47 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA PALMIRO TOGLIATTI 57/A</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>SETTE ALESSANDRO</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="H45" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="H45" s="12" t="n">
+      <c r="I45" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="I45" s="12" t="n">
+      <c r="J45" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="J45" s="12" t="n">
+      <c r="K45" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K45" s="12" t="n">
+      <c r="L45" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="L45" s="12" t="n">
+      <c r="M45" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="M45" s="12" t="n">
+      <c r="N45" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2702,42 +2893,47 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>GUARISCO ADELINO</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>154</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="H46" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="H46" s="12" t="n">
+      <c r="I46" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I46" s="12" t="n">
+      <c r="J46" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="J46" s="12" t="n">
+      <c r="K46" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K46" s="12" t="n">
+      <c r="L46" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L46" s="12" t="n">
+      <c r="M46" s="12" t="n">
         <v>248</v>
       </c>
-      <c r="M46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="N46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2756,42 +2952,47 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA NAZIONALE MONTEDECORO</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>132</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="H47" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H47" s="12" t="n">
+      <c r="I47" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="I47" s="12" t="n">
+      <c r="J47" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="J47" s="12" t="n">
+      <c r="K47" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="K47" s="12" t="n">
+      <c r="L47" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L47" s="12" t="n">
+      <c r="M47" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="M47" s="12" t="n">
+      <c r="N47" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2810,42 +3011,47 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>S .S.114 KM. 79+727 - VIALE DELLO JONIO  21</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="F48" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="H48" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="J48" s="12" t="n">
+      <c r="K48" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="K48" s="12" t="n">
+      <c r="L48" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L48" s="12" t="n">
+      <c r="M48" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="M48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="N48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2864,42 +3070,47 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA UMBERTO BONINO, 1</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
           <t>GUARISCO ADELINO</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>198</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="H49" s="12" t="n">
+      <c r="I49" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="I49" s="12" t="n">
+      <c r="J49" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="J49" s="12" t="n">
+      <c r="K49" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="K49" s="12" t="n">
+      <c r="L49" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L49" s="12" t="n">
+      <c r="M49" s="12" t="n">
         <v>263</v>
       </c>
-      <c r="M49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="N49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2918,42 +3129,47 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>S.S.113 KM.53+563</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
           <t>CASSATA FULVIA</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="H50" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H50" s="12" t="n">
+      <c r="I50" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="I50" s="12" t="n">
+      <c r="J50" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="J50" s="12" t="n">
+      <c r="K50" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="K50" s="12" t="n">
+      <c r="L50" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L50" s="12" t="n">
+      <c r="M50" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="M50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="N50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2972,42 +3188,47 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t xml:space="preserve">VIA PLINIO </t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
           <t>MIELE NICOLINA</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="H51" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H51" s="12" t="n">
+      <c r="I51" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I51" s="12" t="n">
+      <c r="J51" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="J51" s="12" t="n">
+      <c r="K51" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="K51" s="12" t="n">
+      <c r="L51" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L51" s="12" t="n">
+      <c r="M51" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="M51" s="12" t="n">
+      <c r="N51" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3026,42 +3247,47 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>SS 18 KM 72+800</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
           <t>ASCIONE DANIELE</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="G52" s="12" t="n">
+      <c r="H52" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H52" s="12" t="n">
+      <c r="I52" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I52" s="12" t="n">
+      <c r="J52" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="J52" s="12" t="n">
+      <c r="K52" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K52" s="12" t="n">
+      <c r="L52" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="L52" s="12" t="n">
+      <c r="M52" s="12" t="n">
         <v>141</v>
       </c>
-      <c r="M52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="N52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3080,42 +3306,47 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA CRISTOFORO COLOMBO, 4</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="F53" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="G53" s="12" t="n">
+      <c r="H53" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H53" s="12" t="n">
+      <c r="I53" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I53" s="12" t="n">
+      <c r="J53" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="J53" s="12" t="n">
+      <c r="K53" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="K53" s="12" t="n">
+      <c r="L53" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="L53" s="12" t="n">
+      <c r="M53" s="12" t="n">
         <v>188</v>
       </c>
-      <c r="M53" s="12" t="n">
+      <c r="N53" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3134,42 +3365,47 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIALE MADDALENA</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="G54" s="12" t="n">
+      <c r="H54" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="H54" s="12" t="n">
+      <c r="I54" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="I54" s="12" t="n">
+      <c r="J54" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="J54" s="12" t="n">
+      <c r="K54" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K54" s="12" t="n">
+      <c r="L54" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="L54" s="12" t="n">
+      <c r="M54" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="M54" s="12" t="n">
+      <c r="N54" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3188,42 +3424,47 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA MEDICI CONTRADA CANNAMELATA</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
           <t>CASSATA FULVIA</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>132</v>
       </c>
-      <c r="G55" s="12" t="n">
+      <c r="H55" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="H55" s="12" t="n">
+      <c r="I55" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I55" s="12" t="n">
+      <c r="J55" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="J55" s="12" t="n">
+      <c r="K55" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K55" s="12" t="n">
+      <c r="L55" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L55" s="12" t="n">
+      <c r="M55" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="M55" s="12" t="n">
+      <c r="N55" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="O55" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3242,42 +3483,47 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>SS113 KM205 LOCALITA BUON FORNELLO</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
           <t>CASSATA FULVIA</t>
         </is>
       </c>
-      <c r="E56" s="12" t="n">
+      <c r="F56" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="F56" s="12" t="n">
+      <c r="G56" s="12" t="n">
         <v>109</v>
       </c>
-      <c r="G56" s="12" t="n">
+      <c r="H56" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H56" s="12" t="n">
+      <c r="I56" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I56" s="12" t="n">
+      <c r="J56" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="J56" s="12" t="n">
+      <c r="K56" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K56" s="12" t="n">
+      <c r="L56" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="L56" s="12" t="n">
+      <c r="M56" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="M56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="N56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3296,42 +3542,47 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA NAZIONALE SS.113 KM.126+947  SNC</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>CASSATA FULVIA</t>
         </is>
       </c>
-      <c r="E57" s="12" t="n">
+      <c r="F57" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="F57" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="H57" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="J57" s="12" t="n">
+      <c r="K57" s="12" t="n">
         <v>16</v>
-      </c>
-      <c r="K57" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="L57" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="N57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3350,42 +3601,47 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIALE KENNEDY</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
-      <c r="E58" s="12" t="n">
+      <c r="F58" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="F58" s="12" t="n">
+      <c r="G58" s="12" t="n">
         <v>176</v>
       </c>
-      <c r="G58" s="12" t="n">
+      <c r="H58" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H58" s="12" t="n">
+      <c r="I58" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="12" t="n">
+      <c r="J58" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="J58" s="12" t="n">
+      <c r="K58" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K58" s="12" t="n">
+      <c r="L58" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="L58" s="12" t="n">
+      <c r="M58" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="M58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="N58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3404,42 +3660,47 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>SS 6 KM 172+300</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
           <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
-      <c r="E59" s="12" t="n">
+      <c r="F59" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="F59" s="12" t="n">
+      <c r="G59" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="G59" s="12" t="n">
+      <c r="H59" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H59" s="12" t="n">
+      <c r="I59" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I59" s="12" t="n">
+      <c r="J59" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="J59" s="12" t="n">
+      <c r="K59" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K59" s="12" t="n">
+      <c r="L59" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="L59" s="12" t="n">
+      <c r="M59" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="M59" s="12" t="n">
+      <c r="N59" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N59" s="2" t="inlineStr">
+      <c r="O59" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3458,42 +3719,47 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>USCITA PER SCHETTINO</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
           <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
-      <c r="E60" s="12" t="n">
+      <c r="F60" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="F60" s="12" t="n">
+      <c r="G60" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="G60" s="12" t="n">
+      <c r="H60" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H60" s="12" t="n">
+      <c r="I60" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I60" s="12" t="n">
+      <c r="J60" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="J60" s="12" t="n">
+      <c r="K60" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K60" s="12" t="n">
+      <c r="L60" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L60" s="12" t="n">
+      <c r="M60" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="M60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
+      <c r="N60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3512,42 +3778,47 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA GIUSTINO FORTUNATO SNC</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
-      <c r="E61" s="12" t="n">
+      <c r="F61" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="F61" s="12" t="n">
+      <c r="G61" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="G61" s="12" t="n">
+      <c r="H61" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H61" s="12" t="n">
+      <c r="I61" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I61" s="12" t="n">
+      <c r="J61" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="J61" s="12" t="n">
+      <c r="K61" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K61" s="12" t="n">
+      <c r="L61" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L61" s="12" t="n">
+      <c r="M61" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="M61" s="12" t="n">
+      <c r="N61" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N61" s="2" t="inlineStr">
+      <c r="O61" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3566,42 +3837,47 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA BITRITTO KM 4+197</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>RENNA MARCO</t>
         </is>
       </c>
-      <c r="E62" s="12" t="n">
+      <c r="F62" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="F62" s="12" t="n">
+      <c r="G62" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="G62" s="12" t="n">
+      <c r="H62" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H62" s="12" t="n">
+      <c r="I62" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="I62" s="12" t="n">
+      <c r="J62" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="J62" s="12" t="n">
+      <c r="K62" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K62" s="12" t="n">
+      <c r="L62" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L62" s="12" t="n">
+      <c r="M62" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="M62" s="12" t="n">
+      <c r="N62" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N62" s="2" t="inlineStr">
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3620,42 +3896,47 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>S.S. 100 KM. 20+123</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
           <t>TESORO DAVIDE</t>
         </is>
       </c>
-      <c r="E63" s="12" t="n">
+      <c r="F63" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="F63" s="12" t="n">
+      <c r="G63" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G63" s="12" t="n">
+      <c r="H63" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H63" s="12" t="n">
+      <c r="I63" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I63" s="12" t="n">
+      <c r="J63" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="J63" s="12" t="n">
+      <c r="K63" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K63" s="12" t="n">
+      <c r="L63" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L63" s="12" t="n">
+      <c r="M63" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="M63" s="12" t="n">
+      <c r="N63" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3674,20 +3955,22 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>C. DA PASTERIA</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
           <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
-      <c r="E64" s="12" t="n">
+      <c r="F64" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="F64" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G64" s="12" t="n">
         <v>0</v>
       </c>
@@ -3695,21 +3978,24 @@
         <v>0</v>
       </c>
       <c r="I64" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="J64" s="12" t="n">
+      <c r="K64" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K64" s="12" t="n">
+      <c r="L64" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L64" s="12" t="n">
+      <c r="M64" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="M64" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="N64" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3728,42 +4014,47 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>BRUNO BUOZZI N</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
           <t>RENNA MARCO</t>
         </is>
       </c>
-      <c r="E65" s="12" t="n">
+      <c r="F65" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F65" s="12" t="n">
+      <c r="G65" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="G65" s="12" t="n">
+      <c r="H65" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H65" s="12" t="n">
+      <c r="I65" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I65" s="12" t="n">
+      <c r="J65" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="J65" s="12" t="n">
+      <c r="K65" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K65" s="12" t="n">
+      <c r="L65" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L65" s="12" t="n">
+      <c r="M65" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="M65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" s="2" t="inlineStr">
+      <c r="N65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3782,42 +4073,47 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>CORSO ITALIA  SNC</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
           <t>MIELE NICOLINA</t>
         </is>
       </c>
-      <c r="E66" s="12" t="n">
+      <c r="F66" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F66" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G66" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H66" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I66" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="J66" s="12" t="n">
+      <c r="K66" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K66" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L66" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="M66" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
+      <c r="N66" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3836,42 +4132,47 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIALE DEGLI AVIATORI 108/B</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
-      <c r="E67" s="12" t="n">
+      <c r="F67" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="F67" s="12" t="n">
+      <c r="G67" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="G67" s="12" t="n">
+      <c r="H67" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H67" s="12" t="n">
+      <c r="I67" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I67" s="12" t="n">
+      <c r="J67" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="J67" s="12" t="n">
+      <c r="K67" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K67" s="12" t="n">
+      <c r="L67" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L67" s="12" t="n">
+      <c r="M67" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="M67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" s="2" t="inlineStr">
+      <c r="N67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3890,42 +4191,47 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA ACQUICELLA PORTO 5</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
-      <c r="E68" s="12" t="n">
+      <c r="F68" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="F68" s="12" t="n">
+      <c r="G68" s="12" t="n">
         <v>111</v>
-      </c>
-      <c r="G68" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="H68" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I68" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J68" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="J68" s="12" t="n">
+      <c r="K68" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K68" s="12" t="n">
+      <c r="L68" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L68" s="12" t="n">
+      <c r="M68" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="M68" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
+      <c r="N68" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3944,42 +4250,47 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>LOCALITA' FANTINA</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
-      <c r="E69" s="12" t="n">
+      <c r="F69" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F69" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H69" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J69" s="12" t="n">
+      <c r="K69" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K69" s="12" t="n">
+      <c r="L69" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L69" s="12" t="n">
+      <c r="M69" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="M69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" s="2" t="inlineStr">
+      <c r="N69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3998,42 +4309,47 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>S.S.93 PER CANOSA KM.2+746 SN</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>SETTE ALESSANDRO</t>
         </is>
       </c>
-      <c r="E70" s="12" t="n">
+      <c r="F70" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F70" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H70" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="J70" s="12" t="n">
+      <c r="K70" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K70" s="12" t="n">
+      <c r="L70" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L70" s="12" t="n">
+      <c r="M70" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="M70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
+      <c r="N70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4052,42 +4368,47 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA NICOLETTI</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
-      <c r="E71" s="12" t="n">
+      <c r="F71" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="F71" s="12" t="n">
+      <c r="G71" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="G71" s="12" t="n">
+      <c r="H71" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H71" s="12" t="n">
+      <c r="I71" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I71" s="12" t="n">
+      <c r="J71" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="J71" s="12" t="n">
+      <c r="K71" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K71" s="12" t="n">
+      <c r="L71" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L71" s="12" t="n">
+      <c r="M71" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="M71" s="12" t="n">
+      <c r="N71" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N71" s="2" t="inlineStr">
+      <c r="O71" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4106,42 +4427,47 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA PONTE CRATI SNC</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>NEFZI DALILA</t>
         </is>
       </c>
-      <c r="E72" s="12" t="n">
+      <c r="F72" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="F72" s="12" t="n">
+      <c r="G72" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="G72" s="12" t="n">
+      <c r="H72" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H72" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="J72" s="12" t="n">
+      <c r="K72" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K72" s="12" t="n">
+      <c r="L72" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L72" s="12" t="n">
+      <c r="M72" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="M72" s="12" t="n">
+      <c r="N72" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N72" s="2" t="inlineStr">
+      <c r="O72" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4160,42 +4486,47 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>SS.114 KM. 15+417</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
-      <c r="E73" s="12" t="n">
+      <c r="F73" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F73" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H73" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="J73" s="12" t="n">
+      <c r="K73" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K73" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="M73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
+      <c r="N73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4214,42 +4545,47 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>S.S.19 KM.86+200,.  SNC,</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>ASCIONE DANIELE</t>
         </is>
       </c>
-      <c r="E74" s="12" t="n">
+      <c r="F74" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F74" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H74" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="J74" s="12" t="n">
+      <c r="K74" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K74" s="12" t="n">
+      <c r="L74" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="L74" s="12" t="n">
+      <c r="M74" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="M74" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" s="2" t="inlineStr">
+      <c r="N74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4268,42 +4604,47 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>S.S. 115 KM. 407+254 C/DA PANTANELLI S.N.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>LO MONACO GIUSEPPINA</t>
         </is>
       </c>
-      <c r="E75" s="12" t="n">
+      <c r="F75" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F75" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H75" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J75" s="12" t="n">
+      <c r="K75" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K75" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="M75" s="12" t="n">
+      <c r="N75" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N75" s="2" t="inlineStr">
+      <c r="O75" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4322,42 +4663,47 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA A. DORIA</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
           <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
-      <c r="E76" s="12" t="n">
+      <c r="F76" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F76" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H76" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J76" s="12" t="n">
+      <c r="K76" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K76" s="12" t="n">
+      <c r="L76" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L76" s="12" t="n">
+      <c r="M76" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="M76" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
+      <c r="N76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4376,42 +4722,47 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA COMUNALE PER CATANIA</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
           <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
-      <c r="E77" s="12" t="n">
+      <c r="F77" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F77" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H77" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="J77" s="12" t="n">
+      <c r="K77" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K77" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="M77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="N77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4430,42 +4781,47 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>SOTTOVIA DUCA DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
           <t>RENNA MARCO</t>
         </is>
       </c>
-      <c r="E78" s="12" t="n">
+      <c r="F78" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F78" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H78" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="12" t="n">
         <v>16</v>
-      </c>
-      <c r="J78" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="K78" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L78" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M78" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="M78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
+      <c r="N78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4484,42 +4840,47 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>S.S.273 KM. 0+483</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
-      <c r="E79" s="12" t="n">
+      <c r="F79" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F79" s="12" t="n">
+      <c r="G79" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="G79" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I79" s="12" t="n">
+      <c r="J79" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="J79" s="12" t="n">
+      <c r="K79" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K79" s="12" t="n">
+      <c r="L79" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L79" s="12" t="n">
+      <c r="M79" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="M79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" s="2" t="inlineStr">
+      <c r="N79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4538,20 +4899,22 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>SAN NICOLA EST</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
           <t>TUFANO MAURIZIO</t>
         </is>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="F80" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F80" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G80" s="12" t="n">
         <v>0</v>
       </c>
@@ -4559,21 +4922,24 @@
         <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="K80" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="L80" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="M80" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="M80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" s="2" t="inlineStr">
+      <c r="N80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4592,42 +4958,47 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>SS.7 KM.633+976 S.N.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
           <t>TESORO DAVIDE</t>
         </is>
       </c>
-      <c r="E81" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F81" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="G81" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H81" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I81" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L81" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="M81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" s="2" t="inlineStr">
+      <c r="N81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4646,42 +5017,47 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIADOTTO FIUMARELLA - VIA GIOACCHINO DA FIORE SN</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>VULCANO EMANUELE</t>
         </is>
       </c>
-      <c r="E82" s="12" t="n">
+      <c r="F82" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F82" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H82" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J82" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="M82" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" s="2" t="inlineStr">
+      <c r="N82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4700,42 +5076,47 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>A19 ADS CARACOLI NORD</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
           <t>PIROZZI SEBASTIANO</t>
         </is>
       </c>
-      <c r="E83" s="12" t="n">
+      <c r="F83" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F83" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H83" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J83" s="12" t="n">
+      <c r="K83" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K83" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="M83" s="12" t="n">
+      <c r="N83" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N83" s="2" t="inlineStr">
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4754,20 +5135,22 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIALE DI VITTORIO SN</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
-      <c r="E84" s="12" t="n">
+      <c r="F84" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F84" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G84" s="12" t="n">
         <v>0</v>
       </c>
@@ -4775,21 +5158,24 @@
         <v>0</v>
       </c>
       <c r="I84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J84" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L84" s="12" t="n">
+      <c r="M84" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="M84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="2" t="inlineStr">
+      <c r="N84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4808,20 +5194,22 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>SS 16 BIS KM 87+230 NORD</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
           <t>RENNA MARCO</t>
         </is>
       </c>
-      <c r="E85" s="12" t="n">
+      <c r="F85" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F85" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G85" s="12" t="n">
         <v>0</v>
       </c>
@@ -4829,21 +5217,24 @@
         <v>0</v>
       </c>
       <c r="I85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J85" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="M85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="N85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4862,29 +5253,31 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>MOLFETTA</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
           <t>SETTE ALESSANDRO</t>
         </is>
       </c>
-      <c r="E86" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="G86" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I86" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J86" s="12" t="n">
         <v>0</v>
       </c>
@@ -4897,7 +5290,10 @@
       <c r="M86" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N86" s="2" t="inlineStr">
+      <c r="N86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4916,29 +5312,31 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIALE LE GIOVANNI XXIII 84</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
           <t>SETTE ALESSANDRO</t>
         </is>
       </c>
-      <c r="E87" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="G87" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I87" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J87" s="12" t="n">
         <v>0</v>
       </c>
@@ -4951,7 +5349,10 @@
       <c r="M87" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N87" s="2" t="inlineStr">
+      <c r="N87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4970,23 +5371,25 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Cali Giuseppe</t>
+          <t>VIA CALABRICITO LOC. BALZA</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
+          <t>Cali Giuseppe</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
           <t>VIAGGI MARCO</t>
         </is>
       </c>
-      <c r="E88" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="G88" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H88" s="12" t="n">
         <v>0</v>
       </c>
@@ -5005,7 +5408,10 @@
       <c r="M88" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N88" s="2" t="inlineStr">
+      <c r="N88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>78</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>9648</v>
+        <v>10088</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7528</v>
+        <v>7862</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2838</v>
+        <v>3024</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>795</v>
+        <v>838</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>770</v>
+        <v>812</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>515</v>
+        <v>551</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>541</v>
+        <v>563</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>720</v>
+        <v>751</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>389</v>
+        <v>428</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="K12" s="12" t="n">
+        <v>103</v>
+      </c>
+      <c r="L12" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="L12" s="12" t="n">
-        <v>90</v>
-      </c>
       <c r="M12" s="12" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>28</v>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>410</v>
+        <v>435</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>96</v>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>54</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>18</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>1</v>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>470</v>
+        <v>509</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>65</v>
@@ -1326,16 +1326,16 @@
         <v>48</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>1</v>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>1</v>
@@ -1432,25 +1432,25 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>70</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>92</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>2</v>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G23" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>176</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="M23" s="12" t="n">
         <v>172</v>
-      </c>
-      <c r="H23" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="I23" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>172</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="M23" s="12" t="n">
-        <v>165</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>1</v>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>28</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>1</v>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08136</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TORRE ANNUNZIATA</t>
+          <t>MILAZZO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>CORSO UMBERTO S S 18</t>
+          <t>VIALE A. GRAMSCI 156/158</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>327</v>
+        <v>262</v>
       </c>
       <c r="H25" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="I25" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I25" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="J25" s="12" t="n">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>276</v>
+        <v>182</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>08136</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MILAZZO</t>
+          <t>TORRE ANNUNZIATA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIALE A. GRAMSCI 156/158</t>
+          <t>CORSO UMBERTO S S 18</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,35 +1723,35 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>258</v>
+        <v>347</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>174</v>
+        <v>287</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>9</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>25</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>2</v>
@@ -1904,35 +1904,35 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1963,35 +1963,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>123</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>13</v>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>08444</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>AVERSA</t>
+          <t>BENEVENTO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIALE KENNEDY ANGOLO VIA JASI</t>
+          <t>LOCALITA' CAPODIMONTE SNC.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,35 +2077,35 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>39512</t>
+          <t>08444</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>AVERSA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA ERNESTO  BASILE 15/17</t>
+          <t>VIALE KENNEDY ANGOLO VIA JASI</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>110</v>
+        <v>246</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>84</v>
+        <v>216</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>54340</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>BENEVENTO</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>LOCALITA' CAPODIMONTE SNC.</t>
+          <t>VIA ERNESTO  BASILE 15/17</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,39 +2195,39 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>183</v>
+        <v>121</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>221</v>
+        <v>87</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2258,28 +2258,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>31</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>41</v>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>0</v>
@@ -2376,28 +2376,28 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>31</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>2</v>
@@ -2411,17 +2411,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>29688</t>
+          <t>08164</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>PATTI</t>
+          <t>POMIGLIANO D'ARCO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA PAPA GIOVANNI XIII  SN</t>
+          <t>VIA NAZIONALE DELLE PUGLIE</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,56 +2431,56 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>102</v>
+        <v>218</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08164</t>
+          <t>29688</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>POMIGLIANO D'ARCO</t>
+          <t>PATTI</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE DELLE PUGLIE</t>
+          <t>VIA PAPA GIOVANNI XIII  SN</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,39 +2490,39 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>206</v>
+        <v>112</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2553,35 +2553,35 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2612,35 +2612,35 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2671,28 +2671,28 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>66</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>32</v>
@@ -2730,28 +2730,28 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L43" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>0</v>
@@ -2765,17 +2765,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>09092</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>ANDRIA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>STADERA POGGIOREALE</t>
+          <t>VIA PALMIRO TOGLIATTI 57/A</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,35 +2785,35 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>SETTE ALESSANDRO</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2824,17 +2824,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>09092</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>ANDRIA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIA PALMIRO TOGLIATTI 57/A</t>
+          <t>STADERA POGGIOREALE</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,39 +2844,39 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
         <v>105</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2907,28 +2907,28 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I46" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>0</v>
@@ -2942,17 +2942,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE MONTEDECORO</t>
+          <t>S .S.114 KM. 79+727 - VIALE DELLO JONIO  21</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2962,56 +2962,56 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="J47" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="K47" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L47" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M47" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="K47" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="L47" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M47" s="12" t="n">
-        <v>95</v>
-      </c>
       <c r="N47" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>S .S.114 KM. 79+727 - VIALE DELLO JONIO  21</t>
+          <t>VIA UMBERTO BONINO, 1</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,56 +3021,56 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>76</v>
+        <v>276</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>VIA UMBERTO BONINO, 1</t>
+          <t xml:space="preserve">VIA PLINIO </t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,56 +3080,56 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>198</v>
+        <v>91</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>263</v>
+        <v>122</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09719</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>TERME VIGLIATORE</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>S.S.113 KM.53+563</t>
+          <t>VIA NAZIONALE MONTEDECORO</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,35 +3139,35 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3178,17 +3178,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>08964</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>BATTIPAGLIA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIA PLINIO </t>
+          <t>SS 18 KM 72+800</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,56 +3198,56 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="H51" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I51" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I51" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="J51" s="12" t="n">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08964</t>
+          <t>09719</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>BATTIPAGLIA</t>
+          <t>TERME VIGLIATORE</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>SS 18 KM 72+800</t>
+          <t>S.S.113 KM.53+563</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,32 +3257,32 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="N52" s="12" t="n">
         <v>0</v>
@@ -3320,10 +3320,10 @@
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>9</v>
@@ -3332,16 +3332,16 @@
         <v>3</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="N53" s="12" t="n">
         <v>1</v>
@@ -3379,28 +3379,28 @@
         </is>
       </c>
       <c r="F54" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>113</v>
+      </c>
+      <c r="H54" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="I54" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="G54" s="12" t="n">
-        <v>106</v>
-      </c>
-      <c r="H54" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="I54" s="12" t="n">
-        <v>80</v>
-      </c>
       <c r="J54" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="N54" s="12" t="n">
         <v>1</v>
@@ -3414,17 +3414,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09673</t>
+          <t>09992</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SANT'AGATA DI MILITELLO</t>
+          <t>CAMPOFELICE DI ROCCELLA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VIA MEDICI CONTRADA CANNAMELATA</t>
+          <t>SS113 KM205 LOCALITA BUON FORNELLO</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3438,31 +3438,31 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3473,17 +3473,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09992</t>
+          <t>09673</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CAMPOFELICE DI ROCCELLA</t>
+          <t>SANT'AGATA DI MILITELLO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>SS113 KM205 LOCALITA BUON FORNELLO</t>
+          <t>VIA MEDICI CONTRADA CANNAMELATA</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3497,35 +3497,35 @@
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="H56" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I56" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="K56" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I56" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J56" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="K56" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="L56" s="12" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3556,22 +3556,22 @@
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L57" s="12" t="n">
         <v>2</v>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="H58" s="12" t="n">
         <v>3</v>
@@ -3627,16 +3627,16 @@
         <v>2</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="N58" s="12" t="n">
         <v>0</v>
@@ -3674,28 +3674,28 @@
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="N59" s="12" t="n">
         <v>3</v>
@@ -3733,28 +3733,28 @@
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K60" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>0</v>
@@ -3792,28 +3792,28 @@
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H61" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I61" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J61" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="K61" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L61" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I61" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J61" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="K61" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="L61" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="M61" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N61" s="12" t="n">
         <v>9</v>
@@ -3827,17 +3827,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>59427</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>CALATABIANO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>VIA BITRITTO KM 4+197</t>
+          <t>C. DA PASTERIA</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3847,39 +3847,39 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3910,19 +3910,19 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I63" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K63" s="12" t="n">
         <v>15</v>
@@ -3938,24 +3938,24 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CALATABIANO</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>C. DA PASTERIA</t>
+          <t>VIA BITRITTO KM 4+197</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,39 +3965,39 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H65" s="12" t="n">
         <v>4</v>
@@ -4040,16 +4040,16 @@
         <v>14</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L65" s="12" t="n">
         <v>21</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="N65" s="12" t="n">
         <v>0</v>
@@ -4087,28 +4087,28 @@
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N66" s="12" t="n">
         <v>0</v>
@@ -4146,10 +4146,10 @@
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H67" s="12" t="n">
         <v>4</v>
@@ -4158,16 +4158,16 @@
         <v>2</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="N67" s="12" t="n">
         <v>0</v>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H68" s="12" t="n">
         <v>2</v>
@@ -4217,7 +4217,7 @@
         <v>2</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K68" s="12" t="n">
         <v>17</v>
@@ -4226,7 +4226,7 @@
         <v>4</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>0</v>
@@ -4264,22 +4264,22 @@
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L69" s="12" t="n">
         <v>4</v>
@@ -4292,24 +4292,24 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09010</t>
+          <t>09662</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>BARLETTA</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>S.S.93 PER CANOSA KM.2+746 SN</t>
+          <t>SS.114 KM. 15+417</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4319,56 +4319,56 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="N70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>39506</t>
+          <t>09010</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>BARLETTA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>VIA NICOLETTI</t>
+          <t>S.S.93 PER CANOSA KM.2+746 SN</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,56 +4378,56 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
+          <t>SETTE ALESSANDRO</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>08647</t>
+          <t>39506</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLIONE COSENTINO</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTE CRATI SNC</t>
+          <t>VIA NICOLETTI</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,56 +4437,56 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>NEFZI DALILA</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="H72" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I72" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J72" s="12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N72" s="12" t="n">
         <v>12</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>09662</t>
+          <t>08979</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>PADULA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>SS.114 KM. 15+417</t>
+          <t>S.S.19 KM.86+200,.  SNC,</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,56 +4496,56 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>08979</t>
+          <t>08647</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>PADULA</t>
+          <t>CASTIGLIONE COSENTINO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>S.S.19 KM.86+200,.  SNC,</t>
+          <t>VIA PONTE CRATI SNC</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,35 +4555,35 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>NEFZI DALILA</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K74" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4618,19 +4618,19 @@
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K75" s="12" t="n">
         <v>4</v>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N75" s="12" t="n">
         <v>1</v>
@@ -4683,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I76" s="12" t="n">
         <v>0</v>
@@ -4698,14 +4698,14 @@
         <v>1</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4757,14 +4757,14 @@
         <v>0</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
         <v>15</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H79" s="12" t="n">
         <v>0</v>
@@ -4934,14 +4934,14 @@
         <v>4</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="N80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
         <v>12</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H81" s="12" t="n">
         <v>0</v>
@@ -5052,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>78</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>10088</v>
+        <v>10554</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7862</v>
+        <v>8198</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3024</v>
+        <v>3220</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>838</v>
+        <v>871</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>812</v>
+        <v>863</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>551</v>
+        <v>575</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>563</v>
+        <v>585</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>751</v>
+        <v>781</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>507</v>
+        <v>536</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>428</v>
+        <v>485</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>93</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>28</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>435</v>
+        <v>466</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>96</v>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>2</v>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>1</v>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>405</v>
+        <v>428</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>0</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>08046</t>
+          <t>56584</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>POLIGNANO A MARE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CAIO DUILIO FUORIGRO</t>
+          <t>SS ADRIATICA KM 838+890</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>TEDONE VITO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>294</v>
+        <v>60</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>228</v>
+        <v>266</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>274</v>
+        <v>76</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>08046</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SALERNO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA MEDAGLIE D'ORO</t>
+          <t>CAIO DUILIO FUORIGRO</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>328</v>
+        <v>305</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>161</v>
+        <v>239</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>56584</t>
+          <t>53274</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>POLIGNANO A MARE</t>
+          <t>SALERNO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SS ADRIATICA KM 838+890</t>
+          <t>VIA MEDAGLIE D'ORO</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,39 +1428,39 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>TEDONE VITO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>51</v>
+        <v>344</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>250</v>
+        <v>166</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>70</v>
+        <v>330</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>58</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>2</v>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>08970</t>
+          <t>56391</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CAVA DE' TIRRENI</t>
+          <t>MISTERBIANCO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIALE LIBERTA S S 18</t>
+          <t>VIA CARLO MARX 60</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,56 +1546,56 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>180</v>
+        <v>306</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="I23" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>201</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>111</v>
+      </c>
+      <c r="L23" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="J23" s="12" t="n">
-        <v>176</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>83</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>53</v>
-      </c>
       <c r="M23" s="12" t="n">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>56391</t>
+          <t>08970</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MISTERBIANCO</t>
+          <t>CAVA DE' TIRRENI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA CARLO MARX 60</t>
+          <t>VIALE LIBERTA S S 18</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,56 +1605,56 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>285</v>
+        <v>189</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>08136</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>MILAZZO</t>
+          <t>TORRE ANNUNZIATA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIALE A. GRAMSCI 156/158</t>
+          <t>CORSO UMBERTO S S 18</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>262</v>
+        <v>360</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>182</v>
+        <v>299</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>08136</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>TORRE ANNUNZIATA</t>
+          <t>MILAZZO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>CORSO UMBERTO S S 18</t>
+          <t>VIALE A. GRAMSCI 156/158</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,35 +1723,35 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>347</v>
+        <v>275</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>287</v>
+        <v>192</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>9</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
@@ -1821,7 +1821,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>55710</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>MARIANO SEMMOLA 25</t>
+          <t>AGNANO ASTRONI</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1845,42 +1845,42 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>55710</t>
+          <t>55456</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>AGNANO ASTRONI</t>
+          <t>MARIANO SEMMOLA 25</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1904,35 +1904,35 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>138</v>
+        <v>183</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>332</v>
+        <v>372</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1963,52 +1963,52 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>08444</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>AVERSA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>NAZIONALE 102 PER CATANIA</t>
+          <t>VIALE KENNEDY ANGOLO VIA JASI</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,35 +2018,35 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>327</v>
+        <v>257</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>170</v>
+        <v>109</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>21</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>08444</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>AVERSA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIALE KENNEDY ANGOLO VIA JASI</t>
+          <t>NAZIONALE 102 PER CATANIA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,35 +2136,35 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>246</v>
+        <v>343</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>39512</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>SAN GIORGIO A CREMANO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA ERNESTO  BASILE 15/17</t>
+          <t>VIA GIANTURCO</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>121</v>
+        <v>299</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>87</v>
+        <v>242</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SAN GIORGIO A CREMANO</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA GIANTURCO</t>
+          <t>VIA ERNESTO  BASILE 15/17</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>282</v>
+        <v>132</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>232</v>
+        <v>92</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09619</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>FIUMEFREDDO DI SICILIA</t>
+          <t>MARCIANISE</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCONI</t>
+          <t>VIA LEONARDO DA VINCI 14</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,35 +2313,35 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2352,17 +2352,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>09619</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>MARCIANISE</t>
+          <t>FIUMEFREDDO DI SICILIA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA LEONARDO DA VINCI 14</t>
+          <t>VIA MARCONI</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,35 +2372,35 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>189</v>
+        <v>232</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2411,17 +2411,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08164</t>
+          <t>38018</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>POMIGLIANO D'ARCO</t>
+          <t>POTENZA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE DELLE PUGLIE</t>
+          <t>VIA APPIA 187</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,56 +2431,56 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>CAMPANILE EUGENIA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>276</v>
+        <v>141</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>163</v>
+        <v>20</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>29688</t>
+          <t>08164</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PATTI</t>
+          <t>POMIGLIANO D'ARCO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA PAPA GIOVANNI XIII  SN</t>
+          <t>VIA NAZIONALE DELLE PUGLIE</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,56 +2490,56 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>29688</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>POTENZA</t>
+          <t>PATTI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA APPIA 187</t>
+          <t>VIA PAPA GIOVANNI XIII  SN</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>CAMPANILE EUGENIA</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>0</v>
@@ -2612,35 +2612,35 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K41" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M41" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="L41" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>47</v>
-      </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>31</v>
@@ -2692,7 +2692,7 @@
         <v>54</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>32</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>4</v>
@@ -2742,16 +2742,16 @@
         <v>1</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>0</v>
@@ -2765,17 +2765,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>09092</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ANDRIA</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA PALMIRO TOGLIATTI 57/A</t>
+          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,56 +2785,56 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>59</v>
+        <v>275</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>STADERA POGGIOREALE</t>
+          <t>S .S.114 KM. 79+727 - VIALE DELLO JONIO  21</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,35 +2844,35 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2883,17 +2883,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
+          <t>STADERA POGGIOREALE</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,56 +2903,56 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>163</v>
+        <v>66</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>261</v>
+        <v>108</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>09092</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>ANDRIA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>S .S.114 KM. 79+727 - VIALE DELLO JONIO  21</t>
+          <t>VIA PALMIRO TOGLIATTI 57/A</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2962,35 +2962,35 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>SETTE ALESSANDRO</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3001,17 +3001,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>VIA UMBERTO BONINO, 1</t>
+          <t xml:space="preserve">VIA PLINIO </t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,56 +3021,56 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>210</v>
+        <v>97</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I48" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J48" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="K48" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="J48" s="12" t="n">
-        <v>79</v>
-      </c>
-      <c r="K48" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="L48" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>276</v>
+        <v>125</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>SAN GIOVANNI LA PUNTA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIA PLINIO </t>
+          <t>VIA CRISTOFORO COLOMBO, 4</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,56 +3080,56 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>122</v>
+        <v>204</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE MONTEDECORO</t>
+          <t>VIA UMBERTO BONINO, 1</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,35 +3139,35 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>103</v>
+        <v>293</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3178,17 +3178,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>08964</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>BATTIPAGLIA</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>SS 18 KM 72+800</t>
+          <t>VIA NAZIONALE MONTEDECORO</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,35 +3198,35 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3237,17 +3237,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09719</t>
+          <t>08964</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>TERME VIGLIATORE</t>
+          <t>BATTIPAGLIA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>S.S.113 KM.53+563</t>
+          <t>SS 18 KM 72+800</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,32 +3257,32 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="N52" s="12" t="n">
         <v>0</v>
@@ -3296,17 +3296,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>08146</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LA PUNTA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO, 4</t>
+          <t>VIALE MADDALENA</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,32 +3316,32 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="N53" s="12" t="n">
         <v>1</v>
@@ -3355,17 +3355,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>08146</t>
+          <t>09719</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>TERME VIGLIATORE</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>VIALE MADDALENA</t>
+          <t>S.S.113 KM.53+563</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,35 +3375,35 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3438,28 +3438,28 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="H55" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I55" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J55" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K55" s="12" t="n">
         <v>15</v>
-      </c>
-      <c r="I55" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J55" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="K55" s="12" t="n">
-        <v>13</v>
       </c>
       <c r="L55" s="12" t="n">
         <v>35</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="N55" s="12" t="n">
         <v>0</v>
@@ -3497,28 +3497,28 @@
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I56" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K56" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="N56" s="12" t="n">
         <v>1</v>
@@ -3556,22 +3556,22 @@
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L57" s="12" t="n">
         <v>2</v>
@@ -3615,28 +3615,28 @@
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I58" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K58" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="N58" s="12" t="n">
         <v>0</v>
@@ -3674,28 +3674,28 @@
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="N59" s="12" t="n">
         <v>3</v>
@@ -3733,19 +3733,19 @@
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I60" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K60" s="12" t="n">
         <v>13</v>
@@ -3754,31 +3754,31 @@
         <v>3</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>59427</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>CALATABIANO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>VIA GIUSTINO FORTUNATO SNC</t>
+          <t>C. DA PASTERIA</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,56 +3788,56 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="G61" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="H61" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="I61" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J61" s="12" t="n">
-        <v>45</v>
-      </c>
       <c r="K61" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CALATABIANO</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>C. DA PASTERIA</t>
+          <t>S.S. 100 KM. 20+123</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3847,35 +3847,35 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3886,17 +3886,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>S.S. 100 KM. 20+123</t>
+          <t>VIA GIUSTINO FORTUNATO SNC</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3906,20 +3906,20 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J63" s="12" t="n">
         <v>45</v>
@@ -3928,17 +3928,17 @@
         <v>15</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3972,7 +3972,7 @@
         <v>57</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H64" s="12" t="n">
         <v>8</v>
@@ -3990,7 +3990,7 @@
         <v>22</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N64" s="12" t="n">
         <v>2</v>
@@ -4028,25 +4028,25 @@
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M65" s="12" t="n">
         <v>38</v>
@@ -4087,52 +4087,52 @@
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L66" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09298</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>FOGGIA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>VIALE DEGLI AVIATORI 108/B</t>
+          <t>VIA ACQUICELLA PORTO 5</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,32 +4142,32 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I67" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="N67" s="12" t="n">
         <v>0</v>
@@ -4181,17 +4181,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>09298</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>FOGGIA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>VIA ACQUICELLA PORTO 5</t>
+          <t>VIALE DEGLI AVIATORI 108/B</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I68" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>0</v>
@@ -4264,22 +4264,22 @@
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H69" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="K69" s="12" t="n">
         <v>10</v>
-      </c>
-      <c r="I69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="K69" s="12" t="n">
-        <v>9</v>
       </c>
       <c r="L69" s="12" t="n">
         <v>4</v>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4323,35 +4323,35 @@
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="N70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>0</v>
@@ -4394,16 +4394,16 @@
         <v>0</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K71" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N71" s="12" t="n">
         <v>0</v>
@@ -4417,17 +4417,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>39506</t>
+          <t>08979</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>PADULA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>VIA NICOLETTI</t>
+          <t>S.S.19 KM.86+200,.  SNC,</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,56 +4437,56 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H72" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K72" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I72" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J72" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K72" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L72" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>08979</t>
+          <t>08647</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>PADULA</t>
+          <t>CASTIGLIONE COSENTINO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>S.S.19 KM.86+200,.  SNC,</t>
+          <t>VIA PONTE CRATI SNC</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,14 +4496,14 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>NEFZI DALILA</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
         <v>29</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H73" s="12" t="n">
         <v>6</v>
@@ -4512,40 +4512,40 @@
         <v>0</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>08647</t>
+          <t>39506</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLIONE COSENTINO</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTE CRATI SNC</t>
+          <t>VIA NICOLETTI</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,39 +4555,39 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>NEFZI DALILA</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="H74" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I74" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J74" s="12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L74" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M74" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="N74" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="M74" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="N74" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4639,14 +4639,14 @@
         <v>0</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="N75" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4677,19 +4677,19 @@
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K76" s="12" t="n">
         <v>4</v>
@@ -4698,7 +4698,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N76" s="12" t="n">
         <v>0</v>
@@ -4736,19 +4736,19 @@
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K77" s="12" t="n">
         <v>3</v>
@@ -4757,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N77" s="12" t="n">
         <v>0</v>
@@ -4795,28 +4795,28 @@
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L78" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N78" s="12" t="n">
         <v>0</v>
@@ -4857,7 +4857,7 @@
         <v>15</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H79" s="12" t="n">
         <v>0</v>
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G80" s="12" t="n">
         <v>0</v>
@@ -4925,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K80" s="12" t="n">
         <v>1</v>
@@ -4934,7 +4934,7 @@
         <v>4</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N80" s="12" t="n">
         <v>0</v>
@@ -4975,13 +4975,13 @@
         <v>12</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="H81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J81" s="12" t="n">
         <v>5</v>

--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>78</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>10554</v>
+        <v>11109</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>8198</v>
+        <v>8604</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3220</v>
+        <v>3441</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>871</v>
+        <v>916</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>863</v>
+        <v>932</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>575</v>
+        <v>606</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>585</v>
+        <v>613</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>781</v>
+        <v>822</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>536</v>
+        <v>577</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>485</v>
+        <v>550</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>466</v>
+        <v>505</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>96</v>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>394</v>
+        <v>425</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>2</v>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>405</v>
+        <v>438</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09684</t>
+          <t>55861</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>BARCELLONA POZZO DI GOTTO</t>
+          <t>MERCOGLIANO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA PAPA GIOVANNI XXIII N.51.</t>
+          <t>VIA N.SANTANGELO SNC</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,56 +1133,56 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>349</v>
+        <v>451</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>39</v>
+        <v>102</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>134</v>
+        <v>378</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>55861</t>
+          <t>09684</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>MERCOGLIANO</t>
+          <t>BARCELLONA POZZO DI GOTTO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA N.SANTANGELO SNC</t>
+          <t>VIA PAPA GIOVANNI XXIII N.51.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,39 +1192,39 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>428</v>
+        <v>382</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>230</v>
+        <v>291</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>363</v>
+        <v>141</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>525</v>
+        <v>558</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>88</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>56584</t>
+          <t>08046</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>POLIGNANO A MARE</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SS ADRIATICA KM 838+890</t>
+          <t>CAIO DUILIO FUORIGRO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>TEDONE VITO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>76</v>
+        <v>304</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08046</t>
+          <t>53274</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>SALERNO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CAIO DUILIO FUORIGRO</t>
+          <t>VIA MEDAGLIE D'ORO</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>305</v>
+        <v>362</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>239</v>
+        <v>172</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>287</v>
+        <v>347</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>56584</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SALERNO</t>
+          <t>POLIGNANO A MARE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA MEDAGLIE D'ORO</t>
+          <t>SS ADRIATICA KM 838+890</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,39 +1428,39 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>TEDONE VITO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>344</v>
+        <v>61</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>166</v>
+        <v>281</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>330</v>
+        <v>80</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>2</v>
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08970</t>
+          <t>08136</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CAVA DE' TIRRENI</t>
+          <t>TORRE ANNUNZIATA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIALE LIBERTA S S 18</t>
+          <t>CORSO UMBERTO S S 18</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1609,52 +1609,52 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>189</v>
+        <v>378</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>179</v>
+        <v>315</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08136</t>
+          <t>08970</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TORRE ANNUNZIATA</t>
+          <t>CAVA DE' TIRRENI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>CORSO UMBERTO S S 18</t>
+          <t>VIALE LIBERTA S S 18</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1668,52 +1668,52 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>360</v>
+        <v>202</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>299</v>
+        <v>191</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>09651</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MILAZZO</t>
+          <t>VILLAFRANCA TIRRENA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIALE A. GRAMSCI 156/158</t>
+          <t>VILLAFRANCA TIRRENA SNC</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09651</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA</t>
+          <t>MILAZZO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA SNC</t>
+          <t>VIALE A. GRAMSCI 156/158</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1786,42 +1786,42 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>240</v>
+        <v>295</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>55710</t>
+          <t>55456</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>AGNANO ASTRONI</t>
+          <t>MARIANO SEMMOLA 25</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>147</v>
+        <v>194</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>55710</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>MARIANO SEMMOLA 25</t>
+          <t>AGNANO ASTRONI</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>195</v>
+        <v>232</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,35 +1963,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H30" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="K30" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="I30" s="12" t="n">
-        <v>66</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>189</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>86</v>
-      </c>
       <c r="L30" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>2</v>
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>19</v>
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>40</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>13</v>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SAN GIORGIO A CREMANO</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA GIANTURCO</t>
+          <t>VIA ERNESTO  BASILE 15/17</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>299</v>
+        <v>139</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>242</v>
+        <v>98</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>39512</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>SAN GIORGIO A CREMANO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA ERNESTO  BASILE 15/17</t>
+          <t>VIA GIANTURCO</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>132</v>
+        <v>311</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>92</v>
+        <v>249</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>09619</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MARCIANISE</t>
+          <t>FIUMEFREDDO DI SICILIA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA LEONARDO DA VINCI 14</t>
+          <t>VIA MARCONI</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,35 +2313,35 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>202</v>
+        <v>241</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I36" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>138</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="L36" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="J36" s="12" t="n">
-        <v>91</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>65</v>
-      </c>
       <c r="M36" s="12" t="n">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2352,17 +2352,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09619</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>FIUMEFREDDO DI SICILIA</t>
+          <t>MARCIANISE</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCONI</t>
+          <t>VIA LEONARDO DA VINCI 14</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,35 +2372,35 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2435,35 +2435,35 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>29</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2494,28 +2494,28 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
@@ -2571,17 +2571,17 @@
         <v>47</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
@@ -2671,28 +2671,28 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L42" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>32</v>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>4</v>
@@ -2742,16 +2742,16 @@
         <v>1</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>0</v>
@@ -2789,28 +2789,28 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>0</v>
@@ -2860,40 +2860,40 @@
         <v>0</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L45" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>STADERA POGGIOREALE</t>
+          <t>VIA UMBERTO BONINO, 1</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,39 +2903,39 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>66</v>
+        <v>231</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>108</v>
+        <v>314</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2966,28 +2966,28 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G47" s="12" t="n">
+        <v>102</v>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="I47" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="H47" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="I47" s="12" t="n">
-        <v>66</v>
-      </c>
       <c r="J47" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L47" s="12" t="n">
         <v>58</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>1</v>
@@ -3001,17 +3001,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>08964</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>BATTIPAGLIA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIA PLINIO </t>
+          <t>SS 18 KM 72+800</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,56 +3021,56 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>97</v>
+        <v>196</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LA PUNTA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO, 4</t>
+          <t>STADERA POGGIOREALE</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,56 +3080,56 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>161</v>
+        <v>68</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>204</v>
+        <v>108</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIA UMBERTO BONINO, 1</t>
+          <t xml:space="preserve">VIA PLINIO </t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,56 +3139,56 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>214</v>
+        <v>105</v>
       </c>
       <c r="H50" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J50" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="K50" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="L50" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I50" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="J50" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="K50" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="L50" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="M50" s="12" t="n">
-        <v>293</v>
+        <v>133</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>SAN GIOVANNI LA PUNTA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE MONTEDECORO</t>
+          <t>VIA CRISTOFORO COLOMBO, 4</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,35 +3198,35 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="H51" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I51" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="K51" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="I51" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="J51" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="K51" s="12" t="n">
-        <v>29</v>
-      </c>
       <c r="L51" s="12" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>110</v>
+        <v>213</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3237,17 +3237,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08964</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>BATTIPAGLIA</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>SS 18 KM 72+800</t>
+          <t>VIA NAZIONALE MONTEDECORO</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,35 +3257,35 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3320,28 +3320,28 @@
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L53" s="12" t="n">
         <v>47</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="N53" s="12" t="n">
         <v>1</v>
@@ -3379,28 +3379,28 @@
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L54" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N54" s="12" t="n">
         <v>0</v>
@@ -3414,17 +3414,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09992</t>
+          <t>09673</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>CAMPOFELICE DI ROCCELLA</t>
+          <t>SANT'AGATA DI MILITELLO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>SS113 KM205 LOCALITA BUON FORNELLO</t>
+          <t>VIA MEDICI CONTRADA CANNAMELATA</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3438,31 +3438,31 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3473,17 +3473,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09673</t>
+          <t>09992</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SANT'AGATA DI MILITELLO</t>
+          <t>CAMPOFELICE DI ROCCELLA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>VIA MEDICI CONTRADA CANNAMELATA</t>
+          <t>SS113 KM205 LOCALITA BUON FORNELLO</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3497,31 +3497,31 @@
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3556,22 +3556,22 @@
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L57" s="12" t="n">
         <v>2</v>
@@ -3615,28 +3615,28 @@
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I58" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="N58" s="12" t="n">
         <v>0</v>
@@ -3674,28 +3674,28 @@
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I59" s="12" t="n">
         <v>16</v>
       </c>
       <c r="J59" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="K59" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L59" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="K59" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L59" s="12" t="n">
-        <v>34</v>
-      </c>
       <c r="M59" s="12" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="N59" s="12" t="n">
         <v>3</v>
@@ -3709,17 +3709,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>59427</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>PATERNÒ</t>
+          <t>CALATABIANO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>USCITA PER SCHETTINO</t>
+          <t>C. DA PASTERIA</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3729,56 +3729,56 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
         <v>68</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>CALATABIANO</t>
+          <t>PATERNÒ</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>C. DA PASTERIA</t>
+          <t>USCITA PER SCHETTINO</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,56 +3788,56 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="H61" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I61" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I61" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J61" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="N61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>S.S. 100 KM. 20+123</t>
+          <t>VIA GIUSTINO FORTUNATO SNC</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3847,56 +3847,56 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>VIA GIUSTINO FORTUNATO SNC</t>
+          <t>S.S. 100 KM. 20+123</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3906,46 +3906,46 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K63" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>54798</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>VIA BITRITTO KM 4+197</t>
+          <t>BRUNO BUOZZI N</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3969,42 +3969,42 @@
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>54798</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>BRUNO BUOZZI N</t>
+          <t>VIA BITRITTO KM 4+197</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4028,31 +4028,31 @@
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L65" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -4063,17 +4063,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>08013</t>
+          <t>09298</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>ACERRA</t>
+          <t>FOGGIA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>CORSO ITALIA  SNC</t>
+          <t>VIALE DEGLI AVIATORI 108/B</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4083,56 +4083,56 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="H66" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I66" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="K66" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L66" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I66" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="K66" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L66" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="M66" s="12" t="n">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="N66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>08013</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>ACERRA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>VIA ACQUICELLA PORTO 5</t>
+          <t>CORSO ITALIA  SNC</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,56 +4142,56 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="H67" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="K67" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L67" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J67" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="K67" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="L67" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="M67" s="12" t="n">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="N67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09298</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>FOGGIA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>VIALE DEGLI AVIATORI 108/B</t>
+          <t>VIA ACQUICELLA PORTO 5</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
         <v>48</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I68" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>0</v>
@@ -4240,17 +4240,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09315</t>
+          <t>09662</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>CHIEUTI</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>LOCALITA' FANTINA</t>
+          <t>SS.114 KM. 15+417</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4260,56 +4260,56 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09662</t>
+          <t>09315</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>CHIEUTI</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>SS.114 KM. 15+417</t>
+          <t>LOCALITA' FANTINA</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4319,17 +4319,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I70" s="12" t="n">
         <v>0</v>
@@ -4338,13 +4338,13 @@
         <v>37</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N70" s="12" t="n">
         <v>0</v>
@@ -4382,28 +4382,28 @@
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K71" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N71" s="12" t="n">
         <v>0</v>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4500,25 +4500,25 @@
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="H73" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K73" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M73" s="12" t="n">
         <v>25</v>
@@ -4562,7 +4562,7 @@
         <v>29</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H74" s="12" t="n">
         <v>1</v>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>0</v>
@@ -4630,10 +4630,10 @@
         <v>0</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L75" s="12" t="n">
         <v>0</v>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4677,28 +4677,28 @@
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L76" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N76" s="12" t="n">
         <v>0</v>
@@ -4736,19 +4736,19 @@
         </is>
       </c>
       <c r="F77" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="12" t="n">
         <v>21</v>
-      </c>
-      <c r="G77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="I77" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="12" t="n">
-        <v>19</v>
       </c>
       <c r="K77" s="12" t="n">
         <v>3</v>
@@ -4757,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N77" s="12" t="n">
         <v>0</v>
@@ -4816,14 +4816,14 @@
         <v>2</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4934,14 +4934,14 @@
         <v>4</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
         <v>12</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H81" s="12" t="n">
         <v>0</v>
@@ -5052,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>0</v>
@@ -5149,19 +5149,19 @@
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K84" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>78</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>11109</v>
+        <v>11555</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>8604</v>
+        <v>8973</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3441</v>
+        <v>3659</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>916</v>
+        <v>967</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>932</v>
+        <v>974</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>606</v>
+        <v>651</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>613</v>
+        <v>640</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>822</v>
+        <v>858</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>525</v>
+        <v>551</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>577</v>
+        <v>609</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>550</v>
+        <v>607</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,28 +960,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>505</v>
+        <v>532</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>96</v>
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>08182</t>
+          <t>08945</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASTELLAMMARE DI STABIA</t>
+          <t>ANGRI</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIALE EUROPA 87</t>
+          <t>STR PROV ACC AUTOSTR</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>425</v>
+        <v>456</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>207</v>
+        <v>356</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1054,17 +1054,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08945</t>
+          <t>08182</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ANGRI</t>
+          <t>CASTELLAMMARE DI STABIA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>STR PROV ACC AUTOSTR</t>
+          <t>VIALE EUROPA 87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,35 +1074,35 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>341</v>
+        <v>215</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="I16" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>259</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>119</v>
+      </c>
+      <c r="L16" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="J16" s="12" t="n">
-        <v>253</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>116</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>84</v>
-      </c>
       <c r="M16" s="12" t="n">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>0</v>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>42</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>08046</t>
+          <t>53274</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>SALERNO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CAIO DUILIO FUORIGRO</t>
+          <t>VIA MEDAGLIE D'ORO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>330</v>
+        <v>374</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>255</v>
+        <v>180</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>304</v>
+        <v>365</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>56584</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SALERNO</t>
+          <t>POLIGNANO A MARE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA MEDAGLIE D'ORO</t>
+          <t>SS ADRIATICA KM 838+890</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>TEDONE VITO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>362</v>
+        <v>63</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>172</v>
+        <v>293</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>131</v>
+        <v>20</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>347</v>
+        <v>90</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>56584</t>
+          <t>08046</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>POLIGNANO A MARE</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SS ADRIATICA KM 838+890</t>
+          <t>CAIO DUILIO FUORIGRO</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>TEDONE VITO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>61</v>
+        <v>347</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>2</v>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>34</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>2</v>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08136</t>
+          <t>08970</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>TORRE ANNUNZIATA</t>
+          <t>CAVA DE' TIRRENI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CORSO UMBERTO S S 18</t>
+          <t>VIALE LIBERTA S S 18</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1609,52 +1609,52 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>378</v>
+        <v>205</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>315</v>
+        <v>204</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08970</t>
+          <t>09651</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CAVA DE' TIRRENI</t>
+          <t>VILLAFRANCA TIRRENA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIALE LIBERTA S S 18</t>
+          <t>VILLAFRANCA TIRRENA SNC</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>202</v>
+        <v>269</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09651</t>
+          <t>08136</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA</t>
+          <t>TORRE ANNUNZIATA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA SNC</t>
+          <t>CORSO UMBERTO S S 18</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,39 +1723,39 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>257</v>
+        <v>394</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>176</v>
+        <v>337</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>49</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>29</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>36</v>
@@ -1916,19 +1916,19 @@
         <v>19</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>65</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,35 +1963,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
+        <v>212</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>147</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="J30" s="12" t="n">
         <v>203</v>
       </c>
-      <c r="G30" s="12" t="n">
-        <v>138</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>94</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>195</v>
-      </c>
       <c r="K30" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>65</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>44</v>
@@ -2043,7 +2043,7 @@
         <v>75</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>2</v>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>54340</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>BENEVENTO</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>LOCALITA' CAPODIMONTE SNC.</t>
+          <t>NAZIONALE 102 PER CATANIA</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,35 +2077,35 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>215</v>
+        <v>373</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>BENEVENTO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>NAZIONALE 102 PER CATANIA</t>
+          <t>LOCALITA' CAPODIMONTE SNC.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,35 +2136,35 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>363</v>
+        <v>225</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>39512</t>
+          <t>09619</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>FIUMEFREDDO DI SICILIA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA ERNESTO  BASILE 15/17</t>
+          <t>VIA MARCONI</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>139</v>
+        <v>256</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SAN GIORGIO A CREMANO</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA GIANTURCO</t>
+          <t>VIA ERNESTO  BASILE 15/17</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>311</v>
+        <v>148</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>249</v>
+        <v>104</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09619</t>
+          <t>54668</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>FIUMEFREDDO DI SICILIA</t>
+          <t>SAN GIORGIO A CREMANO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCONI</t>
+          <t>VIA GIANTURCO</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,35 +2313,35 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>241</v>
+        <v>321</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>141</v>
+        <v>263</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2376,28 +2376,28 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>2</v>
@@ -2411,17 +2411,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>08164</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>POTENZA</t>
+          <t>POMIGLIANO D'ARCO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA APPIA 187</t>
+          <t>VIA NAZIONALE DELLE PUGLIE</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,56 +2431,56 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>CAMPANILE EUGENIA</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>153</v>
+        <v>329</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>25</v>
+        <v>207</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>85</v>
+        <v>263</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08164</t>
+          <t>38018</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>POMIGLIANO D'ARCO</t>
+          <t>POTENZA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE DELLE PUGLIE</t>
+          <t>VIA APPIA 187</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,39 +2490,39 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>CAMPANILE EUGENIA</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>314</v>
+        <v>164</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>197</v>
+        <v>28</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>249</v>
+        <v>89</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
         <v>33</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>0</v>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
@@ -2647,17 +2647,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>08413</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CAPUA</t>
+          <t>GIARRE</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA FUORI PORTA ROMA</t>
+          <t>PROVINCIALE MACCHIA DI GIARRE</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,35 +2667,35 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2706,17 +2706,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>08413</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>GIARRE</t>
+          <t>CAPUA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>PROVINCIALE MACCHIA DI GIARRE</t>
+          <t>VIA FUORI PORTA ROMA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,35 +2726,35 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>42</v>
@@ -2810,7 +2810,7 @@
         <v>14</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>0</v>
@@ -2824,17 +2824,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>S .S.114 KM. 79+727 - VIALE DELLO JONIO  21</t>
+          <t>VIA UMBERTO BONINO, 1</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,56 +2844,56 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>39</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J45" s="12" t="n">
         <v>101</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>19556</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIA UMBERTO BONINO, 1</t>
+          <t>S .S.114 KM. 79+727 - VIALE DELLO JONIO  21</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,56 +2903,56 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>314</v>
+        <v>101</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>09092</t>
+          <t>08964</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ANDRIA</t>
+          <t>BATTIPAGLIA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>VIA PALMIRO TOGLIATTI 57/A</t>
+          <t>SS 18 KM 72+800</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2962,56 +2962,56 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>66</v>
+        <v>165</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>08964</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>BATTIPAGLIA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>SS 18 KM 72+800</t>
+          <t>STADERA POGGIOREALE</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,56 +3021,56 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>196</v>
+        <v>70</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>STADERA POGGIOREALE</t>
+          <t xml:space="preserve">VIA PLINIO </t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,56 +3080,56 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="G49" s="12" t="n">
         <v>109</v>
       </c>
-      <c r="G49" s="12" t="n">
-        <v>68</v>
-      </c>
       <c r="H49" s="12" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIA PLINIO </t>
+          <t>VIA NAZIONALE MONTEDECORO</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,56 +3139,56 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>09719</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LA PUNTA</t>
+          <t>TERME VIGLIATORE</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO, 4</t>
+          <t>S.S.113 KM.53+563</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,35 +3198,35 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>213</v>
+        <v>92</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3237,17 +3237,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>SAN GIOVANNI LA PUNTA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE MONTEDECORO</t>
+          <t>VIA CRISTOFORO COLOMBO, 4</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,35 +3257,35 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="H52" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J52" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="K52" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="I52" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="J52" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="K52" s="12" t="n">
-        <v>29</v>
-      </c>
       <c r="L52" s="12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>116</v>
+        <v>232</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3296,17 +3296,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08146</t>
+          <t>09092</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>ANDRIA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIALE MADDALENA</t>
+          <t>VIA PALMIRO TOGLIATTI 57/A</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,56 +3316,56 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>SETTE ALESSANDRO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>141</v>
+        <v>66</v>
       </c>
       <c r="N53" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09719</t>
+          <t>08146</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>TERME VIGLIATORE</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>S.S.113 KM.53+563</t>
+          <t>VIALE MADDALENA</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,35 +3375,35 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3438,19 +3438,19 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I55" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="K55" s="12" t="n">
         <v>13</v>
@@ -3459,7 +3459,7 @@
         <v>21</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="N55" s="12" t="n">
         <v>1</v>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="H56" s="12" t="n">
         <v>17</v>
@@ -3515,10 +3515,10 @@
         <v>17</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N56" s="12" t="n">
         <v>0</v>
@@ -3532,17 +3532,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09704</t>
+          <t>09627</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>ACQUEDOLCI</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE SS.113 KM.126+947  SNC</t>
+          <t>VIALE KENNEDY</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,56 +3552,56 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>09627</t>
+          <t>09704</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>ACQUEDOLCI</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>VIALE KENNEDY</t>
+          <t>VIA NAZIONALE SS.113 KM.126+947  SNC</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,39 +3611,39 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="K58" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L58" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J58" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="K58" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L58" s="12" t="n">
-        <v>34</v>
-      </c>
       <c r="M58" s="12" t="n">
-        <v>155</v>
+        <v>2</v>
       </c>
       <c r="N58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3674,28 +3674,28 @@
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="N59" s="12" t="n">
         <v>3</v>
@@ -3733,28 +3733,28 @@
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L60" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>0</v>
@@ -3768,17 +3768,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>PATERNÒ</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>USCITA PER SCHETTINO</t>
+          <t>VIA GIUSTINO FORTUNATO SNC</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,35 +3788,35 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3827,17 +3827,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>PATERNÒ</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>VIA GIUSTINO FORTUNATO SNC</t>
+          <t>USCITA PER SCHETTINO</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3847,35 +3847,35 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H63" s="12" t="n">
         <v>7</v>
@@ -3922,23 +3922,23 @@
         <v>5</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L63" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3969,16 +3969,16 @@
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J64" s="12" t="n">
         <v>37</v>
@@ -3987,7 +3987,7 @@
         <v>5</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M64" s="12" t="n">
         <v>43</v>
@@ -4028,22 +4028,22 @@
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L65" s="12" t="n">
         <v>22</v>
@@ -4087,28 +4087,28 @@
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I66" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L66" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N66" s="12" t="n">
         <v>0</v>
@@ -4122,17 +4122,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>08013</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>ACERRA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>CORSO ITALIA  SNC</t>
+          <t>VIA ACQUICELLA PORTO 5</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,56 +4142,56 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>1</v>
+        <v>154</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="N67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>08013</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>ACERRA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>VIA ACQUICELLA PORTO 5</t>
+          <t>CORSO ITALIA  SNC</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4201,39 +4201,39 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>142</v>
+        <v>1</v>
       </c>
       <c r="H68" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I68" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="K68" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L68" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I68" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J68" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="K68" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="L68" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="M68" s="12" t="n">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4264,28 +4264,28 @@
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G69" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="K69" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="12" t="n">
         <v>22</v>
-      </c>
-      <c r="I69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="K69" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="L69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="12" t="n">
-        <v>20</v>
       </c>
       <c r="N69" s="12" t="n">
         <v>1</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>0</v>
@@ -4341,7 +4341,7 @@
         <v>10</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M70" s="12" t="n">
         <v>7</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4403,31 +4403,31 @@
         <v>10</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>08979</t>
+          <t>08647</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>PADULA</t>
+          <t>CASTIGLIONE COSENTINO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>S.S.19 KM.86+200,.  SNC,</t>
+          <t>VIA PONTE CRATI SNC</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,35 +4437,35 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>NEFZI DALILA</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4476,17 +4476,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>08647</t>
+          <t>08979</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLIONE COSENTINO</t>
+          <t>PADULA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTE CRATI SNC</t>
+          <t>S.S.19 KM.86+200,.  SNC,</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,56 +4496,56 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>NEFZI DALILA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H73" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L73" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>39506</t>
+          <t>09896</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>CARLENTINI</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>VIA NICOLETTI</t>
+          <t>VIA COMUNALE PER CATANIA</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,39 +4555,39 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K75" s="12" t="n">
         <v>5</v>
@@ -4639,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N75" s="12" t="n">
         <v>1</v>
@@ -4653,17 +4653,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>39506</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>VIA A. DORIA</t>
+          <t>VIA NICOLETTI</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4673,56 +4673,56 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="N76" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>09896</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>CARLENTINI</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>VIA COMUNALE PER CATANIA</t>
+          <t>VIA A. DORIA</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4732,39 +4732,39 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="N77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4823,24 +4823,24 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>09242</t>
+          <t>09284</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI ROTONDO</t>
+          <t>MANFREDONIA</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>S.S.273 KM. 0+483</t>
+          <t>VIALE DI VITTORIO SN</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4854,52 +4854,52 @@
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J79" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K79" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L79" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K79" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L79" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="M79" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="N79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>54613</t>
+          <t>09242</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SAN NICOLA LA STRADA</t>
+          <t>SAN GIOVANNI ROTONDO</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>SAN NICOLA EST</t>
+          <t>S.S.273 KM. 0+483</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4909,56 +4909,56 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>TUFANO MAURIZIO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K80" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="N80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>09424</t>
+          <t>54613</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>MASSAFRA</t>
+          <t>SAN NICOLA LA STRADA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>SS.7 KM.633+976 S.N.</t>
+          <t>SAN NICOLA EST</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4968,56 +4968,56 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>TUFANO MAURIZIO</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="H81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>08530</t>
+          <t>09424</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>CATANZARO</t>
+          <t>MASSAFRA</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>VIADOTTO FIUMARELLA - VIA GIOACCHINO DA FIORE SN</t>
+          <t>SS.7 KM.633+976 S.N.</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5027,56 +5027,56 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>VULCANO EMANUELE</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>19805</t>
+          <t>08530</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>TERMINI IMERESE</t>
+          <t>CATANZARO</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>A19 ADS CARACOLI NORD</t>
+          <t>VIADOTTO FIUMARELLA - VIA GIOACCHINO DA FIORE SN</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5086,35 +5086,35 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>PIROZZI SEBASTIANO</t>
+          <t>VULCANO EMANUELE</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N83" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -5125,17 +5125,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>09284</t>
+          <t>19805</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>MANFREDONIA</t>
+          <t>TERMINI IMERESE</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>VIALE DI VITTORIO SN</t>
+          <t>A19 ADS CARACOLI NORD</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>PIROZZI SEBASTIANO</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
@@ -5155,25 +5155,25 @@
         <v>0</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="N84" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="M84" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="N84" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>78</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>11555</v>
+        <v>12070</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>8973</v>
+        <v>9387</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3659</v>
+        <v>3851</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>967</v>
+        <v>993</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>974</v>
+        <v>1008</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>640</v>
+        <v>653</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>858</v>
+        <v>884</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>103</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>609</v>
+        <v>634</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>113</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>607</v>
+        <v>656</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>28</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>405</v>
+        <v>434</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>532</v>
+        <v>554</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>08945</t>
+          <t>08182</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ANGRI</t>
+          <t>CASTELLAMMARE DI STABIA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>STR PROV ACC AUTOSTR</t>
+          <t>VIALE EUROPA 87</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>231</v>
+        <v>284</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>356</v>
+        <v>221</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1054,17 +1054,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08182</t>
+          <t>08945</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CASTELLAMMARE DI STABIA</t>
+          <t>ANGRI</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIALE EUROPA 87</t>
+          <t>STR PROV ACC AUTOSTR</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,35 +1074,35 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>440</v>
+        <v>467</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>271</v>
+        <v>240</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>215</v>
+        <v>376</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>0</v>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>26</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>1</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>08046</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SALERNO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA MEDAGLIE D'ORO</t>
+          <t>CAIO DUILIO FUORIGRO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>180</v>
+        <v>281</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>135</v>
+        <v>41</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>365</v>
+        <v>337</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>56584</t>
+          <t>53274</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>POLIGNANO A MARE</t>
+          <t>SALERNO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SS ADRIATICA KM 838+890</t>
+          <t>VIA MEDAGLIE D'ORO</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>TEDONE VITO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>63</v>
+        <v>385</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>293</v>
+        <v>189</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>90</v>
+        <v>380</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>08046</t>
+          <t>56584</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>POLIGNANO A MARE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CAIO DUILIO FUORIGRO</t>
+          <t>SS ADRIATICA KM 838+890</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>TEDONE VITO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>347</v>
+        <v>67</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>320</v>
+        <v>93</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>55607</t>
+          <t>56391</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>MARIGLIANO</t>
+          <t>MISTERBIANCO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA 11 SETTEMBRE</t>
+          <t>VIA CARLO MARX 60</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,32 +1487,32 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>267</v>
+        <v>39</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>169</v>
+        <v>246</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>423</v>
+        <v>188</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>2</v>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>56391</t>
+          <t>55607</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MISTERBIANCO</t>
+          <t>MARIGLIANO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA CARLO MARX 60</t>
+          <t>VIA 11 SETTEMBRE</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>337</v>
+        <v>405</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>34</v>
+        <v>280</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>232</v>
+        <v>177</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>178</v>
+        <v>444</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>2</v>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08970</t>
+          <t>08136</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CAVA DE' TIRRENI</t>
+          <t>TORRE ANNUNZIATA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIALE LIBERTA S S 18</t>
+          <t>CORSO UMBERTO S S 18</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1609,52 +1609,52 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>205</v>
+        <v>413</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>204</v>
+        <v>358</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09651</t>
+          <t>08970</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA</t>
+          <t>CAVA DE' TIRRENI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA SNC</t>
+          <t>VIALE LIBERTA S S 18</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>08136</t>
+          <t>09651</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>TORRE ANNUNZIATA</t>
+          <t>VILLAFRANCA TIRRENA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>CORSO UMBERTO S S 18</t>
+          <t>VILLAFRANCA TIRRENA SNC</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,39 +1723,39 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>394</v>
+        <v>276</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>337</v>
+        <v>203</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>36</v>
@@ -1798,16 +1798,16 @@
         <v>7</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="H28" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="I28" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="I28" s="12" t="n">
-        <v>29</v>
-      </c>
       <c r="J28" s="12" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>65</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,35 +1963,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>36</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>2</v>
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>13</v>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>24</v>
@@ -2152,16 +2152,16 @@
         <v>76</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>19</v>
@@ -2199,28 +2199,28 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>35</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>0</v>
@@ -2258,35 +2258,35 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="H36" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="I36" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>95</v>
-      </c>
       <c r="J36" s="12" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>41</v>
@@ -2376,28 +2376,28 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>68</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>2</v>
@@ -2435,28 +2435,28 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>53</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
@@ -2497,13 +2497,13 @@
         <v>164</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>79</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>105</v>
@@ -2515,14 +2515,14 @@
         <v>57</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2553,35 +2553,35 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L40" s="12" t="n">
         <v>33</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
@@ -2671,28 +2671,28 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>0</v>
@@ -2706,17 +2706,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>08413</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CAPUA</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA FUORI PORTA ROMA</t>
+          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,35 +2726,35 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>173</v>
+        <v>261</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>123</v>
+        <v>6</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>171</v>
+        <v>320</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2765,17 +2765,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>08413</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>CAPUA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
+          <t>VIA FUORI PORTA ROMA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,35 +2785,35 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>228</v>
+        <v>178</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>6</v>
+        <v>127</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>300</v>
+        <v>179</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2848,31 +2848,31 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>31</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>0</v>
@@ -2919,23 +2919,23 @@
         <v>0</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2966,28 +2966,28 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>18</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>0</v>
@@ -3001,17 +3001,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>09719</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>TERME VIGLIATORE</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>STADERA POGGIOREALE</t>
+          <t>S.S.113 KM.53+563</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,56 +3021,56 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>70</v>
+        <v>181</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="L48" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>SAN GIOVANNI LA PUNTA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIA PLINIO </t>
+          <t>VIA CRISTOFORO COLOMBO, 4</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,17 +3080,17 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>109</v>
+        <v>215</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I49" s="12" t="n">
         <v>5</v>
@@ -3099,37 +3099,37 @@
         <v>88</v>
       </c>
       <c r="K49" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="L49" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L49" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="M49" s="12" t="n">
-        <v>143</v>
+        <v>253</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE MONTEDECORO</t>
+          <t xml:space="preserve">VIA PLINIO </t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,56 +3139,56 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K50" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L50" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="M50" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="N50" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="L50" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="M50" s="12" t="n">
-        <v>127</v>
-      </c>
-      <c r="N50" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09719</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>TERME VIGLIATORE</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>S.S.113 KM.53+563</t>
+          <t>STADERA POGGIOREALE</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,56 +3198,56 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="H51" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="I51" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I51" s="12" t="n">
-        <v>71</v>
-      </c>
       <c r="J51" s="12" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="L51" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LA PUNTA</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO, 4</t>
+          <t>VIA NAZIONALE MONTEDECORO</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,35 +3257,35 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>232</v>
+        <v>129</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3323,13 +3323,13 @@
         <v>110</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>54</v>
@@ -3341,7 +3341,7 @@
         <v>58</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="N53" s="12" t="n">
         <v>1</v>
@@ -3379,28 +3379,28 @@
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="N54" s="12" t="n">
         <v>1</v>
@@ -3438,28 +3438,28 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="N55" s="12" t="n">
         <v>1</v>
@@ -3473,17 +3473,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09992</t>
+          <t>09627</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CAMPOFELICE DI ROCCELLA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>SS113 KM205 LOCALITA BUON FORNELLO</t>
+          <t>VIALE KENNEDY</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,32 +3493,32 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>156</v>
+        <v>220</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L56" s="12" t="n">
         <v>41</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="N56" s="12" t="n">
         <v>0</v>
@@ -3532,17 +3532,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09627</t>
+          <t>09992</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>CAMPOFELICE DI ROCCELLA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>VIALE KENNEDY</t>
+          <t>SS113 KM205 LOCALITA BUON FORNELLO</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,32 +3552,32 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>212</v>
+        <v>167</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>59</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>166</v>
+        <v>110</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L58" s="12" t="n">
         <v>2</v>
@@ -3643,24 +3643,24 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>08423</t>
+          <t>59427</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>VAIRANO PATENORA</t>
+          <t>CALATABIANO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>SS 6 KM 172+300</t>
+          <t>C. DA PASTERIA</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,56 +3670,56 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>168</v>
+        <v>57</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>CALATABIANO</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>C. DA PASTERIA</t>
+          <t>VIA GIUSTINO FORTUNATO SNC</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3729,56 +3729,56 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="H60" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I60" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I60" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J60" s="12" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>08423</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>VAIRANO PATENORA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>VIA GIUSTINO FORTUNATO SNC</t>
+          <t>SS 6 KM 172+300</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,35 +3788,35 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3851,28 +3851,28 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L62" s="12" t="n">
         <v>3</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N62" s="12" t="n">
         <v>0</v>
@@ -3910,35 +3910,35 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3969,28 +3969,28 @@
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K64" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N64" s="12" t="n">
         <v>0</v>
@@ -4028,19 +4028,19 @@
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I65" s="12" t="n">
         <v>33</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K65" s="12" t="n">
         <v>9</v>
@@ -4087,28 +4087,28 @@
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I66" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="N66" s="12" t="n">
         <v>0</v>
@@ -4122,17 +4122,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>09662</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>VIA ACQUICELLA PORTO 5</t>
+          <t>SS.114 KM. 15+417</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,56 +4142,56 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>116</v>
+        <v>25</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>08013</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>ACERRA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>CORSO ITALIA  SNC</t>
+          <t>VIA ACQUICELLA PORTO 5</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4201,56 +4201,56 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>1</v>
+        <v>168</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09662</t>
+          <t>08013</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>ACERRA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>SS.114 KM. 15+417</t>
+          <t>CORSO ITALIA  SNC</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4260,35 +4260,35 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G69" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4323,28 +4323,28 @@
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L70" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N70" s="12" t="n">
         <v>0</v>
@@ -4403,31 +4403,31 @@
         <v>10</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>08647</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLIONE COSENTINO</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTE CRATI SNC</t>
+          <t>VIA A. DORIA</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,39 +4437,39 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>NEFZI DALILA</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G73" s="12" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K73" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N73" s="12" t="n">
         <v>0</v>
@@ -4535,17 +4535,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09896</t>
+          <t>08647</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>CARLENTINI</t>
+          <t>CASTIGLIONE COSENTINO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>VIA COMUNALE PER CATANIA</t>
+          <t>VIA PONTE CRATI SNC</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,39 +4555,39 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>NEFZI DALILA</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>0</v>
@@ -4630,40 +4630,40 @@
         <v>0</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N75" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>39506</t>
+          <t>09896</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>CARLENTINI</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>VIA NICOLETTI</t>
+          <t>VIA COMUNALE PER CATANIA</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4673,56 +4673,56 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>19</v>
       </c>
       <c r="N76" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>39506</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>VIA A. DORIA</t>
+          <t>VIA NICOLETTI</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4732,39 +4732,39 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="K77" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4795,13 +4795,13 @@
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I78" s="12" t="n">
         <v>0</v>
@@ -4813,10 +4813,10 @@
         <v>3</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="N78" s="12" t="n">
         <v>0</v>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
         <v>15</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>4</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
@@ -5034,7 +5034,7 @@
         <v>12</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H82" s="12" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N83" s="12" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>7</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="12" t="n">
         <v>2</v>

--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>78</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>12070</v>
+        <v>12668</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>9387</v>
+        <v>9866</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3851</v>
+        <v>4153</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>993</v>
+        <v>1034</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1008</v>
+        <v>1032</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>659</v>
+        <v>690</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>884</v>
+        <v>918</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>564</v>
+        <v>586</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>634</v>
+        <v>667</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>486</v>
+        <v>521</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>656</v>
+        <v>700</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>08182</t>
+          <t>08945</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CASTELLAMMARE DI STABIA</t>
+          <t>ANGRI</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIALE EUROPA 87</t>
+          <t>STR PROV ACC AUTOSTR</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>457</v>
+        <v>487</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>284</v>
+        <v>244</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>221</v>
+        <v>402</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1054,17 +1054,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08945</t>
+          <t>08182</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ANGRI</t>
+          <t>CASTELLAMMARE DI STABIA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>STR PROV ACC AUTOSTR</t>
+          <t>VIALE EUROPA 87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,35 +1074,35 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>240</v>
+        <v>294</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>376</v>
+        <v>231</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="I16" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>286</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>132</v>
+      </c>
+      <c r="L16" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="J16" s="12" t="n">
-        <v>268</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>124</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>93</v>
-      </c>
       <c r="M16" s="12" t="n">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>0</v>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>1</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>595</v>
+        <v>618</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>08046</t>
+          <t>53274</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>SALERNO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CAIO DUILIO FUORIGRO</t>
+          <t>VIA MEDAGLIE D'ORO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,32 +1310,32 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>369</v>
+        <v>400</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>337</v>
+        <v>393</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>1</v>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>08046</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SALERNO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA MEDAGLIE D'ORO</t>
+          <t>CAIO DUILIO FUORIGRO</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,39 +1369,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>189</v>
+        <v>292</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>141</v>
+        <v>41</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I22" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>264</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>142</v>
+      </c>
+      <c r="L22" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J22" s="12" t="n">
-        <v>246</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>133</v>
-      </c>
-      <c r="L22" s="12" t="n">
-        <v>35</v>
-      </c>
       <c r="M22" s="12" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>2</v>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>2</v>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>6</v>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>1</v>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>0</v>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,35 +1963,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>2</v>
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>13</v>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>54340</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>BENEVENTO</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>LOCALITA' CAPODIMONTE SNC.</t>
+          <t>VIA ERNESTO  BASILE 15/17</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,39 +2136,39 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>227</v>
+        <v>168</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="J33" s="12" t="n">
+        <v>176</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="M33" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="K33" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>261</v>
-      </c>
       <c r="N33" s="12" t="n">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2199,28 +2199,28 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>35</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>0</v>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>39512</t>
+          <t>54340</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>BENEVENTO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA ERNESTO  BASILE 15/17</t>
+          <t>LOCALITA' CAPODIMONTE SNC.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,39 +2254,39 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>157</v>
+        <v>232</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>113</v>
+        <v>281</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>35</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>41</v>
@@ -2376,28 +2376,28 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>2</v>
@@ -2435,31 +2435,31 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2494,52 +2494,52 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>30</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>29688</t>
+          <t>55058</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PATTI</t>
+          <t>GIARRE</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA PAPA GIOVANNI XIII  SN</t>
+          <t>VIA LUIGI STURZO SN</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,56 +2549,56 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>118</v>
+        <v>145</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>55058</t>
+          <t>29688</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>GIARRE</t>
+          <t>PATTI</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA LUIGI STURZO SN</t>
+          <t>VIA PAPA GIOVANNI XIII  SN</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,56 +2608,56 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>59</v>
+        <v>150</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>GIARRE</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>PROVINCIALE MACCHIA DI GIARRE</t>
+          <t>VIA UMBERTO BONINO, 1</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,35 +2667,35 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>209</v>
+        <v>259</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="I42" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="J42" s="12" t="n">
+        <v>125</v>
+      </c>
+      <c r="K42" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L42" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="M42" s="12" t="n">
+        <v>383</v>
+      </c>
+      <c r="N42" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="J42" s="12" t="n">
-        <v>107</v>
-      </c>
-      <c r="K42" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="L42" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="M42" s="12" t="n">
-        <v>185</v>
-      </c>
-      <c r="N42" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2706,17 +2706,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>GIARRE</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
+          <t>PROVINCIALE MACCHIA DI GIARRE</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,32 +2726,32 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>261</v>
+        <v>218</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>320</v>
+        <v>201</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>0</v>
@@ -2765,17 +2765,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>08413</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CAPUA</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA FUORI PORTA ROMA</t>
+          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,35 +2785,35 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>178</v>
+        <v>261</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>127</v>
+        <v>6</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>179</v>
+        <v>343</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2824,17 +2824,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>08413</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>CAPUA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIA UMBERTO BONINO, 1</t>
+          <t>VIA FUORI PORTA ROMA</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,35 +2844,35 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>236</v>
+        <v>184</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>353</v>
+        <v>186</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>0</v>
@@ -2919,16 +2919,16 @@
         <v>0</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>35</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>0</v>
@@ -2942,17 +2942,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>08964</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>BATTIPAGLIA</t>
+          <t>SAN GIOVANNI LA PUNTA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>SS 18 KM 72+800</t>
+          <t>VIA CRISTOFORO COLOMBO, 4</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2962,35 +2962,35 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>175</v>
+        <v>268</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -3001,17 +3001,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09719</t>
+          <t>08964</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>TERME VIGLIATORE</t>
+          <t>BATTIPAGLIA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>S.S.113 KM.53+563</t>
+          <t>SS 18 KM 72+800</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,32 +3021,32 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>181</v>
+        <v>223</v>
       </c>
       <c r="H48" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I48" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="I48" s="12" t="n">
-        <v>74</v>
-      </c>
       <c r="J48" s="12" t="n">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>0</v>
@@ -3060,17 +3060,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>39211</t>
+          <t>09719</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LA PUNTA</t>
+          <t>TERME VIGLIATORE</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>VIA CRISTOFORO COLOMBO, 4</t>
+          <t>S.S.113 KM.53+563</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,35 +3080,35 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>215</v>
+        <v>185</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>253</v>
+        <v>102</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3119,17 +3119,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIA PLINIO </t>
+          <t>VIA NAZIONALE MONTEDECORO</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,56 +3139,56 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>112</v>
+        <v>178</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>09092</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>ANDRIA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>STADERA POGGIOREALE</t>
+          <t>VIA PALMIRO TOGLIATTI 57/A</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,35 +3198,35 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>SETTE ALESSANDRO</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3237,17 +3237,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE MONTEDECORO</t>
+          <t xml:space="preserve">VIA PLINIO </t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,56 +3257,56 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>172</v>
+        <v>115</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="K52" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L52" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="M52" s="12" t="n">
+        <v>157</v>
+      </c>
+      <c r="N52" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="L52" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="M52" s="12" t="n">
-        <v>129</v>
-      </c>
-      <c r="N52" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09092</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>ANDRIA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA PALMIRO TOGLIATTI 57/A</t>
+          <t>STADERA POGGIOREALE</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,35 +3316,35 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
+        <v>113</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="H53" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="I53" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="J53" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="K53" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L53" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M53" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="G53" s="12" t="n">
-        <v>109</v>
-      </c>
-      <c r="H53" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="I53" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="J53" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="K53" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="L53" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="M53" s="12" t="n">
-        <v>70</v>
-      </c>
       <c r="N53" s="12" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3379,28 +3379,28 @@
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N54" s="12" t="n">
         <v>1</v>
@@ -3414,17 +3414,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09673</t>
+          <t>09627</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SANT'AGATA DI MILITELLO</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VIA MEDICI CONTRADA CANNAMELATA</t>
+          <t>VIALE KENNEDY</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,35 +3434,35 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>172</v>
+        <v>224</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3473,17 +3473,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09627</t>
+          <t>09673</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>SANT'AGATA DI MILITELLO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>VIALE KENNEDY</t>
+          <t>VIA MEDICI CONTRADA CANNAMELATA</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,35 +3493,35 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>220</v>
+        <v>179</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3556,10 +3556,10 @@
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="H57" s="12" t="n">
         <v>17</v>
@@ -3568,7 +3568,7 @@
         <v>6</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K57" s="12" t="n">
         <v>17</v>
@@ -3577,7 +3577,7 @@
         <v>41</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>0</v>
@@ -3591,17 +3591,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>09704</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>ACQUEDOLCI</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE SS.113 KM.126+947  SNC</t>
+          <t>VIA GIUSTINO FORTUNATO SNC</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,56 +3611,56 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>09704</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>CALATABIANO</t>
+          <t>ACQUEDOLCI</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>C. DA PASTERIA</t>
+          <t>VIA NAZIONALE SS.113 KM.126+947  SNC</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,56 +3670,56 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="N59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>59427</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>CALATABIANO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>VIA GIUSTINO FORTUNATO SNC</t>
+          <t>C. DA PASTERIA</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3729,56 +3729,56 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>08423</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>VAIRANO PATENORA</t>
+          <t>PATERNÒ</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>SS 6 KM 172+300</t>
+          <t>USCITA PER SCHETTINO</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,35 +3788,35 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>177</v>
+        <v>67</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3827,17 +3827,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>08423</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>PATERNÒ</t>
+          <t>VAIRANO PATENORA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>USCITA PER SCHETTINO</t>
+          <t>SS 6 KM 172+300</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3847,35 +3847,35 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L62" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="M62" s="12" t="n">
+        <v>192</v>
+      </c>
+      <c r="N62" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="M62" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="N62" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>75</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H63" s="12" t="n">
         <v>10</v>
@@ -3931,14 +3931,14 @@
         <v>27</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N63" s="12" t="n">
         <v>17</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3969,28 +3969,28 @@
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K64" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N64" s="12" t="n">
         <v>0</v>
@@ -4004,17 +4004,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>08013</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>ACERRA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>VIA BITRITTO KM 4+197</t>
+          <t>CORSO ITALIA  SNC</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,56 +4024,56 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>09298</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>FOGGIA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>VIALE DEGLI AVIATORI 108/B</t>
+          <t>VIA BITRITTO KM 4+197</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4083,35 +4083,35 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="H66" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I66" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="J66" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="K66" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L66" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M66" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="N66" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="J66" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="K66" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L66" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M66" s="12" t="n">
-        <v>105</v>
-      </c>
-      <c r="N66" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -4122,17 +4122,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09662</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>SS.114 KM. 15+417</t>
+          <t>VIA ACQUICELLA PORTO 5</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,56 +4142,56 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>1</v>
+        <v>192</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>09298</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>FOGGIA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>VIA ACQUICELLA PORTO 5</t>
+          <t>VIALE DEGLI AVIATORI 108/B</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4201,17 +4201,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I68" s="12" t="n">
         <v>2</v>
@@ -4220,13 +4220,13 @@
         <v>55</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>0</v>
@@ -4240,17 +4240,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>08013</t>
+          <t>09662</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>ACERRA</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>CORSO ITALIA  SNC</t>
+          <t>SS.114 KM. 15+417</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4260,39 +4260,39 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G69" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="I69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4344,31 +4344,31 @@
         <v>6</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09010</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>BARLETTA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>S.S.93 PER CANOSA KM.2+746 SN</t>
+          <t>VIA A. DORIA</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,56 +4378,56 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>09010</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>BARLETTA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>VIA A. DORIA</t>
+          <t>S.S.93 PER CANOSA KM.2+746 SN</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,32 +4437,32 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>SETTE ALESSANDRO</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="N72" s="12" t="n">
         <v>0</v>
@@ -4476,17 +4476,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>08979</t>
+          <t>19873</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>PADULA</t>
+          <t>SIRACUSA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>S.S.19 KM.86+200,.  SNC,</t>
+          <t>S.S. 115 KM. 407+254 C/DA PANTANELLI S.N.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>LO MONACO GIUSEPPINA</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
@@ -4506,25 +4506,25 @@
         <v>0</v>
       </c>
       <c r="H73" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K73" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="K73" s="12" t="n">
+      <c r="L73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="N73" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="L73" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="M73" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="N73" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4535,17 +4535,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>08647</t>
+          <t>08979</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLIONE COSENTINO</t>
+          <t>PADULA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTE CRATI SNC</t>
+          <t>S.S.19 KM.86+200,.  SNC,</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,56 +4555,56 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>NEFZI DALILA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I74" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>08647</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>SIRACUSA</t>
+          <t>CASTIGLIONE COSENTINO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>S.S. 115 KM. 407+254 C/DA PANTANELLI S.N.</t>
+          <t>VIA PONTE CRATI SNC</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4614,39 +4614,39 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>LO MONACO GIUSEPPINA</t>
+          <t>NEFZI DALILA</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H75" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I75" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I75" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J75" s="12" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4739,13 +4739,13 @@
         <v>29</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H77" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J77" s="12" t="n">
         <v>16</v>
@@ -4771,17 +4771,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>38047</t>
+          <t>09284</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>MANFREDONIA</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>SOTTOVIA DUCA DEGLI ABRUZZI</t>
+          <t>VIALE DI VITTORIO SN</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4791,32 +4791,32 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K78" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K78" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="L78" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="N78" s="12" t="n">
         <v>0</v>
@@ -4830,17 +4830,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>09284</t>
+          <t>38047</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>MANFREDONIA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>VIALE DI VITTORIO SN</t>
+          <t>SOTTOVIA DUCA DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4850,32 +4850,32 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="12" t="n">
         <v>19</v>
-      </c>
-      <c r="G79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="I79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="12" t="n">
-        <v>18</v>
       </c>
       <c r="K79" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="N79" s="12" t="n">
         <v>0</v>
@@ -4916,7 +4916,7 @@
         <v>15</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>4</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
@@ -5007,17 +5007,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09424</t>
+          <t>08530</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>MASSAFRA</t>
+          <t>CATANZARO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>SS.7 KM.633+976 S.N.</t>
+          <t>VIADOTTO FIUMARELLA - VIA GIOACCHINO DA FIORE SN</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5027,56 +5027,56 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>VULCANO EMANUELE</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
         <v>12</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>08530</t>
+          <t>09424</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>CATANZARO</t>
+          <t>MASSAFRA</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>VIADOTTO FIUMARELLA - VIA GIOACCHINO DA FIORE SN</t>
+          <t>SS.7 KM.633+976 S.N.</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5086,39 +5086,39 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>VULCANO EMANUELE</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="H83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="G83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I83" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J83" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="N83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>78</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>12668</v>
+        <v>13314</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>9866</v>
+        <v>10383</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4153</v>
+        <v>4461</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,35 +842,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1034</v>
+        <v>1067</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1032</v>
+        <v>1072</v>
       </c>
       <c r="H11" s="12" t="n">
+        <v>720</v>
+      </c>
+      <c r="I11" s="12" t="n">
         <v>690</v>
       </c>
-      <c r="I11" s="12" t="n">
-        <v>665</v>
-      </c>
       <c r="J11" s="12" t="n">
-        <v>918</v>
+        <v>950</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>586</v>
+        <v>605</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>667</v>
+        <v>716</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>521</v>
+        <v>562</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>700</v>
+        <v>752</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>458</v>
+        <v>486</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>575</v>
+        <v>593</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>08945</t>
+          <t>55861</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ANGRI</t>
+          <t>MERCOGLIANO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>STR PROV ACC AUTOSTR</t>
+          <t>VIA N.SANTANGELO SNC</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>D'AMBROSIO RAFFAELLO</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>402</v>
+        <v>444</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>3</v>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>55861</t>
+          <t>08945</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>MERCOGLIANO</t>
+          <t>ANGRI</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA N.SANTANGELO SNC</t>
+          <t>STR PROV ACC AUTOSTR</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,35 +1133,35 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>09684</t>
+          <t>08078</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>BARCELLONA POZZO DI GOTTO</t>
+          <t>CASORIA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA PAPA GIOVANNI XXIII N.51.</t>
+          <t>VIA A.DIAZ</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,56 +1192,56 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>420</v>
+        <v>387</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>48</v>
+        <v>447</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>29</v>
+        <v>644</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>306</v>
+        <v>264</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>171</v>
+        <v>265</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>1</v>
+        <v>197</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>08078</t>
+          <t>09684</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CASORIA</t>
+          <t>BARCELLONA POZZO DI GOTTO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA A.DIAZ</t>
+          <t>VIA PAPA GIOVANNI XXIII N.51.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,35 +1251,35 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>377</v>
+        <v>444</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>426</v>
+        <v>53</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>618</v>
+        <v>32</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>247</v>
+        <v>320</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>255</v>
+        <v>188</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>189</v>
+        <v>1</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>27</v>
@@ -1326,19 +1326,19 @@
         <v>22</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>71</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>41</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>17</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>397</v>
+        <v>421</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>39</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>2</v>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>2</v>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>6</v>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08970</t>
+          <t>09651</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CAVA DE' TIRRENI</t>
+          <t>VILLAFRANCA TIRRENA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIALE LIBERTA S S 18</t>
+          <t>VILLAFRANCA TIRRENA SNC</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>224</v>
+        <v>295</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09651</t>
+          <t>08970</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA</t>
+          <t>CAVA DE' TIRRENI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA TIRRENA SNC</t>
+          <t>VIALE LIBERTA S S 18</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,35 +1723,35 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>292</v>
+        <v>234</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>54</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
@@ -1845,42 +1845,42 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>31</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>37</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>55710</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>AGNANO ASTRONI</t>
+          <t>VIA A FALCONE 224</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1904,52 +1904,52 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>259</v>
+        <v>170</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>397</v>
+        <v>191</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIA A FALCONE 224</t>
+          <t>VIA ERNESTO  BASILE 15/17</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,35 +1959,35 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="I30" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="K30" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="J30" s="12" t="n">
-        <v>216</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>100</v>
-      </c>
       <c r="L30" s="12" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>08444</t>
+          <t>55710</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>AVERSA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIALE KENNEDY ANGOLO VIA JASI</t>
+          <t>AGNANO ASTRONI</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,56 +2018,56 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>307</v>
+        <v>264</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>263</v>
+        <v>408</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>08444</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>AVERSA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>NAZIONALE 102 PER CATANIA</t>
+          <t>VIALE KENNEDY ANGOLO VIA JASI</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,35 +2077,35 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>CONTE DOMENICO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>405</v>
+        <v>324</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>206</v>
+        <v>130</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>39512</t>
+          <t>09619</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>FIUMEFREDDO DI SICILIA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA ERNESTO  BASILE 15/17</t>
+          <t>VIA MARCONI</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>168</v>
+        <v>282</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>09619</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>FIUMEFREDDO DI SICILIA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCONI</t>
+          <t>NAZIONALE 102 PER CATANIA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2199,31 +2199,31 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>275</v>
+        <v>415</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>157</v>
+        <v>285</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2258,28 +2258,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>19</v>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="H36" s="12" t="n">
+        <v>113</v>
+      </c>
+      <c r="I36" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>105</v>
-      </c>
       <c r="J36" s="12" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>41</v>
@@ -2376,28 +2376,28 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>46</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>70</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>2</v>
@@ -2435,31 +2435,31 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>58</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2494,35 +2494,35 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>32</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2553,28 +2553,28 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L40" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>0</v>
@@ -2612,52 +2612,52 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
+        <v>167</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>124</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="M41" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="G41" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>120</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>150</v>
-      </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>GIARRE</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA UMBERTO BONINO, 1</t>
+          <t>PROVINCIALE MACCHIA DI GIARRE</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,35 +2667,35 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>383</v>
+        <v>213</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2706,17 +2706,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>GIARRE</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>PROVINCIALE MACCHIA DI GIARRE</t>
+          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,32 +2726,32 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>218</v>
+        <v>261</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>201</v>
+        <v>366</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
+          <t>VIA UMBERTO BONINO, 1</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2789,31 +2789,31 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>343</v>
+        <v>403</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2848,28 +2848,28 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>32</v>
@@ -2907,35 +2907,35 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2966,28 +2966,28 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L47" s="12" t="n">
         <v>29</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>2</v>
@@ -3001,17 +3001,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>08964</t>
+          <t>09719</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>BATTIPAGLIA</t>
+          <t>TERME VIGLIATORE</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>SS 18 KM 72+800</t>
+          <t>S.S.113 KM.53+563</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,32 +3021,32 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>180</v>
+        <v>105</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>0</v>
@@ -3060,17 +3060,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09719</t>
+          <t>08964</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>TERME VIGLIATORE</t>
+          <t>BATTIPAGLIA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>S.S.113 KM.53+563</t>
+          <t>SS 18 KM 72+800</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,32 +3080,32 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>102</v>
+        <v>192</v>
       </c>
       <c r="N49" s="12" t="n">
         <v>0</v>
@@ -3143,28 +3143,28 @@
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L50" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="N50" s="12" t="n">
         <v>1</v>
@@ -3202,28 +3202,28 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N51" s="12" t="n">
         <v>1</v>
@@ -3261,52 +3261,52 @@
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I52" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K52" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="L52" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="L52" s="12" t="n">
-        <v>27</v>
-      </c>
       <c r="M52" s="12" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="N52" s="12" t="n">
         <v>31</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08063</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>STADERA POGGIOREALE</t>
+          <t>VIA GIUSTINO FORTUNATO SNC</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,35 +3316,35 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -3355,17 +3355,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>08146</t>
+          <t>09627</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>VIALE MADDALENA</t>
+          <t>VIALE KENNEDY</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,35 +3375,35 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>161</v>
+        <v>237</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3414,17 +3414,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09627</t>
+          <t>08063</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>VIALE KENNEDY</t>
+          <t>STADERA POGGIOREALE</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>224</v>
+        <v>73</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3497,28 +3497,28 @@
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K56" s="12" t="n">
         <v>14</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="N56" s="12" t="n">
         <v>1</v>
@@ -3532,17 +3532,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09992</t>
+          <t>08146</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CAMPOFELICE DI ROCCELLA</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>SS113 KM205 LOCALITA BUON FORNELLO</t>
+          <t>VIALE MADDALENA</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,35 +3552,35 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>VOZZOLO ROSARIO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>113</v>
+        <v>168</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3591,17 +3591,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>09992</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>CAMPOFELICE DI ROCCELLA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>VIA GIUSTINO FORTUNATO SNC</t>
+          <t>SS113 KM205 LOCALITA BUON FORNELLO</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,39 +3611,39 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>127</v>
+        <v>184</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3674,22 +3674,22 @@
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L59" s="12" t="n">
         <v>2</v>
@@ -3733,35 +3733,35 @@
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L60" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3792,28 +3792,28 @@
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I61" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N61" s="12" t="n">
         <v>0</v>
@@ -3851,28 +3851,28 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K62" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="N62" s="12" t="n">
         <v>3</v>
@@ -3886,17 +3886,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09139</t>
+          <t>54798</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>CASAMASSIMA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>S.S. 100 KM. 20+123</t>
+          <t>BRUNO BUOZZI N</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3906,35 +3906,35 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>TESORO DAVIDE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3945,17 +3945,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>54798</t>
+          <t>09139</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>CASAMASSIMA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>BRUNO BUOZZI N</t>
+          <t>S.S. 100 KM. 20+123</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,56 +3965,56 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>TESORO DAVIDE</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H64" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I64" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J64" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="K64" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L64" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="I64" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J64" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="K64" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L64" s="12" t="n">
-        <v>38</v>
-      </c>
       <c r="M64" s="12" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>08013</t>
+          <t>19554</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>ACERRA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>CORSO ITALIA  SNC</t>
+          <t>VIA ACQUICELLA PORTO 5</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,56 +4024,56 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>1</v>
+        <v>199</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="K65" s="12" t="n">
         <v>21</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>68</v>
+        <v>149</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>09662</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>VIA BITRITTO KM 4+197</t>
+          <t>SS.114 KM. 15+417</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4083,56 +4083,56 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>125</v>
+        <v>1</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>08013</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>ACERRA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>VIA ACQUICELLA PORTO 5</t>
+          <t>CORSO ITALIA  SNC</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,56 +4142,56 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>192</v>
+        <v>1</v>
       </c>
       <c r="H67" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="K67" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="L67" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J67" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="K67" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="L67" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="M67" s="12" t="n">
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="N67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09298</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>FOGGIA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>VIALE DEGLI AVIATORI 108/B</t>
+          <t>VIA BITRITTO KM 4+197</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4201,35 +4201,35 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="H68" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I68" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="J68" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="K68" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L68" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M68" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="N68" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="J68" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="K68" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L68" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="M68" s="12" t="n">
-        <v>110</v>
-      </c>
-      <c r="N68" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4240,17 +4240,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09662</t>
+          <t>09298</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>FOGGIA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>SS.114 KM. 15+417</t>
+          <t>VIALE DEGLI AVIATORI 108/B</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4260,39 +4260,39 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4323,52 +4323,52 @@
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>09010</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>BARLETTA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>VIA A. DORIA</t>
+          <t>S.S.93 PER CANOSA KM.2+746 SN</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,56 +4378,56 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>SETTE ALESSANDRO</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="N71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>09010</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>BARLETTA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>S.S.93 PER CANOSA KM.2+746 SN</t>
+          <t>VIA A. DORIA</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,32 +4437,32 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="I72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="K72" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L72" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L72" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="M72" s="12" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N72" s="12" t="n">
         <v>0</v>
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G73" s="12" t="n">
         <v>0</v>
@@ -4512,7 +4512,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K73" s="12" t="n">
         <v>6</v>
@@ -4521,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="N73" s="12" t="n">
         <v>1</v>
@@ -4535,17 +4535,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>08979</t>
+          <t>08647</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>PADULA</t>
+          <t>CASTIGLIONE COSENTINO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>S.S.19 KM.86+200,.  SNC,</t>
+          <t>VIA PONTE CRATI SNC</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,56 +4555,56 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>NEFZI DALILA</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I74" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>08647</t>
+          <t>08979</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLIONE COSENTINO</t>
+          <t>PADULA</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTE CRATI SNC</t>
+          <t>S.S.19 KM.86+200,.  SNC,</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4614,39 +4614,39 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>NEFZI DALILA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I75" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4677,19 +4677,19 @@
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K76" s="12" t="n">
         <v>5</v>
@@ -4698,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N76" s="12" t="n">
         <v>0</v>
@@ -4739,7 +4739,7 @@
         <v>29</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H77" s="12" t="n">
         <v>1</v>
@@ -4795,22 +4795,22 @@
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L78" s="12" t="n">
         <v>1</v>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4875,14 +4875,14 @@
         <v>3</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4916,7 +4916,7 @@
         <v>15</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>4</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
@@ -5052,14 +5052,14 @@
         <v>0</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
         <v>7</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H84" s="12" t="n">
         <v>2</v>

--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>CONTE DOMENICO</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>D'AMBROSIO RAFFAELLO</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>VOZZOLO ROSARIO</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">

--- a/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Cali Giuseppe.xlsx
@@ -684,13 +684,13 @@
         <v>78</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>13314</v>
+        <v>13206</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>10383</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>4461</v>
+        <v>4384</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1072</v>
+        <v>1054</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>605</v>
@@ -863,14 +863,14 @@
         <v>111</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>562</v>
+        <v>549</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>129</v>
@@ -913,7 +913,7 @@
         <v>229</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>433</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>148</v>
@@ -922,10 +922,10 @@
         <v>116</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>593</v>
+        <v>576</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>431</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>237</v>
@@ -981,14 +981,14 @@
         <v>52</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>143</v>
@@ -1040,31 +1040,31 @@
         <v>103</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>08182</t>
+          <t>08945</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CASTELLAMMARE DI STABIA</t>
+          <t>ANGRI</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIALE EUROPA 87</t>
+          <t>STR PROV ACC AUTOSTR</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>242</v>
+        <v>403</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08945</t>
+          <t>08182</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ANGRI</t>
+          <t>CASTELLAMMARE DI STABIA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>STR PROV ACC AUTOSTR</t>
+          <t>VIALE EUROPA 87</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1137,35 +1137,35 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>506</v>
+        <v>470</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>62</v>
+        <v>132</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>160</v>
+        <v>89</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>417</v>
+        <v>240</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>644</v>
+        <v>630</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>111</v>
@@ -1217,14 +1217,14 @@
         <v>96</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>32</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>144</v>
@@ -1276,14 +1276,14 @@
         <v>39</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>71</v>
@@ -1335,7 +1335,7 @@
         <v>152</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -1373,19 +1373,19 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>54</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>130</v>
@@ -1394,7 +1394,7 @@
         <v>41</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>3</v>
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>79</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>17</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>121</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>100</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>151</v>
@@ -1512,10 +1512,10 @@
         <v>39</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>73</v>
@@ -1571,7 +1571,7 @@
         <v>103</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>2</v>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>14</v>
@@ -1621,7 +1621,7 @@
         <v>6</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>67</v>
@@ -1630,7 +1630,7 @@
         <v>51</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>6</v>
@@ -1671,7 +1671,7 @@
         <v>275</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>45</v>
@@ -1680,7 +1680,7 @@
         <v>13</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>84</v>
@@ -1689,7 +1689,7 @@
         <v>50</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>08970</t>
+          <t>55456</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CAVA DE' TIRRENI</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIALE LIBERTA S S 18</t>
+          <t>MARIANO SEMMOLA 25</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,35 +1723,35 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>243</v>
+        <v>462</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>08970</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>MILAZZO</t>
+          <t>CAVA DE' TIRRENI</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIALE A. GRAMSCI 156/158</t>
+          <t>VIALE LIBERTA S S 18</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>GUARISCO ADELINO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
         <v>268</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>329</v>
+        <v>225</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>265</v>
+        <v>235</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>55456</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>MILAZZO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>MARIANO SEMMOLA 25</t>
+          <t>VIALE A. GRAMSCI 156/158</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,39 +1841,39 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>PASTORE PIERLUIGI</t>
+          <t>GUARISCO ADELINO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
+        <v>259</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>321</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="L28" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="M28" s="12" t="n">
         <v>262</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>257</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>234</v>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>108</v>
-      </c>
-      <c r="L28" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="M28" s="12" t="n">
-        <v>468</v>
-      </c>
       <c r="N28" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,19 +1904,19 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>86</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>113</v>
@@ -1925,10 +1925,10 @@
         <v>14</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>39512</t>
+          <t>55710</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>PALERMO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIA ERNESTO  BASILE 15/17</t>
+          <t>AGNANO ASTRONI</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,56 +1959,56 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>181</v>
+        <v>261</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>142</v>
+        <v>402</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>55710</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>PALERMO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>AGNANO ASTRONI</t>
+          <t>VIA ERNESTO  BASILE 15/17</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,39 +2018,39 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>PASTORE PIERLUIGI</t>
+          <t>LICCIARDELLO AMANDA GINEVRA VERON</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>264</v>
+        <v>180</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>408</v>
+        <v>139</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2081,19 +2081,19 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>35</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>52</v>
@@ -2102,7 +2102,7 @@
         <v>90</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>2</v>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>09619</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>FIUMEFREDDO DI SICILIA</t>
+          <t>ACIREALE</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCONI</t>
+          <t>NAZIONALE 102 PER CATANIA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2140,31 +2140,31 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>282</v>
+        <v>409</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="I33" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="L33" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="J33" s="12" t="n">
-        <v>178</v>
-      </c>
-      <c r="K33" s="12" t="n">
-        <v>72</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>36</v>
-      </c>
       <c r="M33" s="12" t="n">
-        <v>172</v>
+        <v>280</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>56553</t>
+          <t>09619</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ACIREALE</t>
+          <t>FIUMEFREDDO DI SICILIA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>NAZIONALE 102 PER CATANIA</t>
+          <t>VIA MARCONI</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2199,31 +2199,31 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>415</v>
+        <v>279</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>285</v>
+        <v>167</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2258,19 +2258,19 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>80</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>57</v>
@@ -2279,10 +2279,10 @@
         <v>71</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>69</v>
@@ -2338,10 +2338,10 @@
         <v>36</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2352,17 +2352,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>18432</t>
+          <t>08164</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>MARCIANISE</t>
+          <t>POMIGLIANO D'ARCO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA LEONARDO DA VINCI 14</t>
+          <t>VIA NAZIONALE DELLE PUGLIE</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,32 +2372,32 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>LANZANTE DOMENICO</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>269</v>
+        <v>358</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>46</v>
+        <v>235</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>198</v>
+        <v>307</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>2</v>
@@ -2411,17 +2411,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08164</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>POMIGLIANO D'ARCO</t>
+          <t>MARCIANISE</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE DELLE PUGLIE</t>
+          <t>VIA LEONARDO DA VINCI 14</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,32 +2431,32 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
+        <v>191</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>264</v>
+      </c>
+      <c r="H38" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="L38" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="M38" s="12" t="n">
         <v>195</v>
-      </c>
-      <c r="G38" s="12" t="n">
-        <v>369</v>
-      </c>
-      <c r="H38" s="12" t="n">
-        <v>123</v>
-      </c>
-      <c r="I38" s="12" t="n">
-        <v>238</v>
-      </c>
-      <c r="J38" s="12" t="n">
-        <v>141</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>313</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>2</v>
@@ -2494,19 +2494,19 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>33</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>32</v>
@@ -2515,31 +2515,31 @@
         <v>74</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>55058</t>
+          <t>29688</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>GIARRE</t>
+          <t>PATTI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA LUIGI STURZO SN</t>
+          <t>VIA PAPA GIOVANNI XIII  SN</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,56 +2549,56 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>64</v>
+        <v>157</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>29688</t>
+          <t>55063</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>PATTI</t>
+          <t>GIARRE</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA PAPA GIOVANNI XIII  SN</t>
+          <t>PROVINCIALE MACCHIA DI GIARRE</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,46 +2608,46 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>2</v>
+        <v>214</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>158</v>
+        <v>209</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>55058</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>PROVINCIALE MACCHIA DI GIARRE</t>
+          <t>VIA LUIGI STURZO SN</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2674,39 +2674,39 @@
         <v>160</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>213</v>
+        <v>64</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>39403</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
+          <t>VIA UMBERTO BONINO, 1</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2730,31 +2730,31 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>366</v>
+        <v>397</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>39403</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA UMBERTO BONINO, 1</t>
+          <t>VIALE GIOSTRA ANGOLO VIA ABETONE SNC</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2789,31 +2789,31 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>403</v>
+        <v>353</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2848,19 +2848,19 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>39</v>
@@ -2869,10 +2869,10 @@
         <v>61</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2907,19 +2907,19 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>38</v>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H47" s="12" t="n">
         <v>18</v>
@@ -2978,7 +2978,7 @@
         <v>5</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>38</v>
@@ -2987,7 +2987,7 @@
         <v>29</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>2</v>
@@ -3001,17 +3001,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>09719</t>
+          <t>08964</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>TERME VIGLIATORE</t>
+          <t>BATTIPAGLIA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>S.S.113 KM.53+563</t>
+          <t>SS 18 KM 72+800</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,32 +3021,32 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>81</v>
+        <v>16</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>105</v>
+        <v>189</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>0</v>
@@ -3060,17 +3060,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>08964</t>
+          <t>09092</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>BATTIPAGLIA</t>
+          <t>ANDRIA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>SS 18 KM 72+800</t>
+          <t>VIA PALMIRO TOGLIATTI 57/A</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,56 +3080,56 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>SETTE ALESSANDRO</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>229</v>
+        <v>122</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>192</v>
+        <v>80</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>54615</t>
+          <t>08194</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>MADDALONI</t>
+          <t>POMPEI</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE MONTEDECORO</t>
+          <t xml:space="preserve">VIA PLINIO </t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,56 +3139,56 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>LANZANTE DOMENICO</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>186</v>
+        <v>116</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09092</t>
+          <t>09719</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>ANDRIA</t>
+          <t>TERME VIGLIATORE</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>VIA PALMIRO TOGLIATTI 57/A</t>
+          <t>S.S.113 KM.53+563</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,56 +3198,56 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
         <v>123</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08194</t>
+          <t>54615</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>POMPEI</t>
+          <t>MADDALONI</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIA PLINIO </t>
+          <t>VIA NAZIONALE MONTEDECORO</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,56 +3257,56 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>LANZANTE DOMENICO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09237</t>
+          <t>08146</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SAN SEVERO</t>
+          <t>NAPOLI</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA GIUSTINO FORTUNATO SNC</t>
+          <t>VIALE MADDALENA</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,39 +3316,39 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>PASTORE PIERLUIGI</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>21</v>
@@ -3391,7 +3391,7 @@
         <v>2</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>17</v>
@@ -3400,7 +3400,7 @@
         <v>41</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="N54" s="12" t="n">
         <v>0</v>
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>49</v>
@@ -3450,7 +3450,7 @@
         <v>18</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="K55" s="12" t="n">
         <v>55</v>
@@ -3466,24 +3466,24 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09673</t>
+          <t>09237</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SANT'AGATA DI MILITELLO</t>
+          <t>SAN SEVERO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>VIA MEDICI CONTRADA CANNAMELATA</t>
+          <t>VIA GIUSTINO FORTUNATO SNC</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,56 +3493,56 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>188</v>
+        <v>132</v>
       </c>
       <c r="H56" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="I56" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="I56" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J56" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="K56" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="L56" s="12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>08146</t>
+          <t>09673</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>NAPOLI</t>
+          <t>SANT'AGATA DI MILITELLO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>VIALE MADDALENA</t>
+          <t>VIA MEDICI CONTRADA CANNAMELATA</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,32 +3552,32 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>PASTORE PIERLUIGI</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>1</v>
@@ -3627,7 +3627,7 @@
         <v>7</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K58" s="12" t="n">
         <v>17</v>
@@ -3650,17 +3650,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>09704</t>
+          <t>59427</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>ACQUEDOLCI</t>
+          <t>CALATABIANO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE SS.113 KM.126+947  SNC</t>
+          <t>C. DA PASTERIA</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,32 +3670,32 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>CASSATA FULVIA</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="N59" s="12" t="n">
         <v>0</v>
@@ -3709,17 +3709,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>09704</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>CALATABIANO</t>
+          <t>ACQUEDOLCI</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>C. DA PASTERIA</t>
+          <t>VIA NAZIONALE SS.113 KM.126+947  SNC</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3729,32 +3729,32 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>CASSATA FULVIA</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>0</v>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H61" s="12" t="n">
         <v>12</v>
@@ -3804,7 +3804,7 @@
         <v>4</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="K61" s="12" t="n">
         <v>18</v>
@@ -3813,7 +3813,7 @@
         <v>6</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N61" s="12" t="n">
         <v>0</v>
@@ -3851,19 +3851,19 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H62" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K62" s="12" t="n">
         <v>13</v>
@@ -3872,7 +3872,7 @@
         <v>41</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N62" s="12" t="n">
         <v>3</v>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G63" s="12" t="n">
         <v>96</v>
@@ -3922,7 +3922,7 @@
         <v>24</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K63" s="12" t="n">
         <v>5</v>
@@ -3931,7 +3931,7 @@
         <v>41</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N63" s="12" t="n">
         <v>0</v>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H64" s="12" t="n">
         <v>11</v>
@@ -3981,7 +3981,7 @@
         <v>6</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K64" s="12" t="n">
         <v>20</v>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H65" s="12" t="n">
         <v>3</v>
@@ -4040,7 +4040,7 @@
         <v>4</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="K65" s="12" t="n">
         <v>21</v>
@@ -4049,7 +4049,7 @@
         <v>5</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="N65" s="12" t="n">
         <v>1</v>
@@ -4063,17 +4063,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>09662</t>
+          <t>09119</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>MESSINA</t>
+          <t>BARI</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>SS.114 KM. 15+417</t>
+          <t>VIA BITRITTO KM 4+197</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4083,56 +4083,56 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>MONTISANTI GIUSEPPE</t>
+          <t>RENNA MARCO</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
         <v>68</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>1</v>
+        <v>127</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>08013</t>
+          <t>09298</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>ACERRA</t>
+          <t>FOGGIA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>CORSO ITALIA  SNC</t>
+          <t>VIALE DEGLI AVIATORI 108/B</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,56 +4142,56 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>MIELE NICOLINA</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
         <v>68</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="N67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09119</t>
+          <t>09662</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>BARI</t>
+          <t>MESSINA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>VIA BITRITTO KM 4+197</t>
+          <t>SS.114 KM. 15+417</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4201,56 +4201,56 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>RENNA MARCO</t>
+          <t>MONTISANTI GIUSEPPE</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="N68" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09298</t>
+          <t>08013</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>FOGGIA</t>
+          <t>ACERRA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>VIALE DEGLI AVIATORI 108/B</t>
+          <t>CORSO ITALIA  SNC</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4260,39 +4260,39 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>MIELE NICOLINA</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="N69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>3</v>
@@ -4335,7 +4335,7 @@
         <v>3</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K70" s="12" t="n">
         <v>17</v>
@@ -4358,17 +4358,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09010</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>BARLETTA</t>
+          <t>CATANIA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>S.S.93 PER CANOSA KM.2+746 SN</t>
+          <t>VIA A. DORIA</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,56 +4378,56 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>SETTE ALESSANDRO</t>
+          <t>ARMELLINI GIACOMO</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="I71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K71" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L71" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L71" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="M71" s="12" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="N71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>08647</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>CATANIA</t>
+          <t>CASTIGLIONE COSENTINO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>VIA A. DORIA</t>
+          <t>VIA PONTE CRATI SNC</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,39 +4437,39 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>ARMELLINI GIACOMO</t>
+          <t>NEFZI DALILA</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G73" s="12" t="n">
         <v>0</v>
@@ -4512,7 +4512,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K73" s="12" t="n">
         <v>6</v>
@@ -4521,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N73" s="12" t="n">
         <v>1</v>
@@ -4535,17 +4535,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>08647</t>
+          <t>09010</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>CASTIGLIONE COSENTINO</t>
+          <t>BARLETTA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTE CRATI SNC</t>
+          <t>S.S.93 PER CANOSA KM.2+746 SN</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,56 +4555,56 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>NEFZI DALILA</t>
+          <t>SETTE ALESSANDRO</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K74" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>08979</t>
+          <t>09896</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>PADULA</t>
+          <t>CARLENTINI</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>S.S.19 KM.86+200,.  SNC,</t>
+          <t>VIA COMUNALE PER CATANIA</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4614,32 +4614,32 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>ASCIONE DANIELE</t>
+          <t>DIADEMA VITO MANUEL</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N75" s="12" t="n">
         <v>0</v>
@@ -4653,17 +4653,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>09896</t>
+          <t>08979</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>CARLENTINI</t>
+          <t>PADULA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>VIA COMUNALE PER CATANIA</t>
+          <t>S.S.19 KM.86+200,.  SNC,</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4673,32 +4673,32 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>DIADEMA VITO MANUEL</t>
+          <t>ASCIONE DANIELE</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N76" s="12" t="n">
         <v>0</v>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H77" s="12" t="n">
         <v>1</v>
@@ -4748,7 +4748,7 @@
         <v>9</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K77" s="12" t="n">
         <v>6</v>
@@ -4757,10 +4757,10 @@
         <v>14</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>0</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K78" s="12" t="n">
         <v>7</v>
@@ -4816,14 +4816,14 @@
         <v>1</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G79" s="12" t="n">
         <v>1</v>
@@ -4866,7 +4866,7 @@
         <v>0</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K79" s="12" t="n">
         <v>3</v>
@@ -4875,14 +4875,14 @@
         <v>3</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4913,19 +4913,19 @@
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K80" s="12" t="n">
         <v>1</v>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G81" s="12" t="n">
         <v>0</v>
@@ -4984,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K81" s="12" t="n">
         <v>1</v>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G82" s="12" t="n">
         <v>0</v>
@@ -5043,7 +5043,7 @@
         <v>0</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K82" s="12" t="n">
         <v>1</v>
@@ -5052,14 +5052,14 @@
         <v>0</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H83" s="12" t="n">
         <v>0</v>
@@ -5102,7 +5102,7 @@
         <v>8</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K83" s="12" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         <v>6</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N83" s="12" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K84" s="12" t="n">
         <v>1</v>
@@ -5170,14 +5170,14 @@
         <v>0</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N84" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85" s="12" t="n">
         <v>0</v>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H86" s="12" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H88" s="12" t="n">
         <v>0</v>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
